--- a/results/interim_results/pmf_results/allsites_pmf_bs_fpeak.xlsx
+++ b/results/interim_results/pmf_results/allsites_pmf_bs_fpeak.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drexel0-my.sharepoint.com/personal/lf649_drexel_edu/Documents/Research/South Philly R21/Papers/Analysis Paper/thriveair_analysis/results/interim_results/pmf_results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lf649/git_repos/active/thriveair_analysis/results/interim_results/pmf_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7BC9AA7-5D2A-41D3-BEB4-50DB1F2C0D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381C32B6-68FD-FD4E-9138-E6AC149E32A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="3360" windowWidth="17625" windowHeight="10650" activeTab="4" xr2:uid="{DDB22B41-BAF4-440D-839D-9D7FB0427160}"/>
+    <workbookView xWindow="14860" yWindow="6580" windowWidth="21800" windowHeight="11220" activeTab="5" xr2:uid="{BE83C13A-3955-4331-9143-64E0083985C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Factor 1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Factor 3" sheetId="3" r:id="rId3"/>
     <sheet name="Factor 4" sheetId="4" r:id="rId4"/>
     <sheet name="Factor 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Key" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="43">
   <si>
     <t>Species</t>
   </si>
@@ -123,16 +124,16 @@
     <t>trichloromonofluoromethane</t>
   </si>
   <si>
-    <t>Fpeak Value conc</t>
+    <t>Fpeak Value_conc</t>
   </si>
   <si>
-    <t>BS 5th conc</t>
+    <t>BS 5th_conc</t>
   </si>
   <si>
-    <t>BS Median conc</t>
+    <t>BS Median_conc</t>
   </si>
   <si>
-    <t>BS 95th conc</t>
+    <t>BS 95th_conc</t>
   </si>
   <si>
     <t>Fpeak Value pct</t>
@@ -145,6 +146,30 @@
   </si>
   <si>
     <t>BS 95th pct</t>
+  </si>
+  <si>
+    <t>Factor Number</t>
+  </si>
+  <si>
+    <t>Percent Mass explained</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Gasoline evaporation</t>
+  </si>
+  <si>
+    <t>Petroleum solvents</t>
+  </si>
+  <si>
+    <t>Background/Legacy</t>
+  </si>
+  <si>
+    <t>Vehicle exhaust</t>
+  </si>
+  <si>
+    <t>Auto repair industry</t>
   </si>
 </sst>
 </file>
@@ -180,8 +205,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -515,11 +541,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2C583B-1116-45D0-BB3C-BFAB416F470F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F381CA0D-A984-4B31-BD67-67D4D79C1842}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -548,758 +574,758 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9.2452000000000006E-2</v>
+        <v>0.23433000000000001</v>
       </c>
       <c r="C2">
-        <v>6.07905110246394E-2</v>
+        <v>0.20333576291146899</v>
       </c>
       <c r="D2">
-        <v>9.07249901996008E-2</v>
+        <v>0.23650971326516201</v>
       </c>
       <c r="E2">
-        <v>0.13394173526634301</v>
+        <v>0.26729856543900599</v>
       </c>
       <c r="F2">
-        <v>9.9874696731567401</v>
+        <v>23.3832302093506</v>
       </c>
       <c r="G2">
-        <v>5.5628463582798799</v>
+        <v>19.665276039453801</v>
       </c>
       <c r="H2">
-        <v>8.9370499093300495</v>
+        <v>23.266280319629701</v>
       </c>
       <c r="I2">
-        <v>13.315772436658699</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>26.706593381755699</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5.5541E-2</v>
+        <v>7.1820999999999996E-2</v>
       </c>
       <c r="C3">
-        <v>3.9012606210876898E-2</v>
+        <v>5.14418339916465E-2</v>
       </c>
       <c r="D3">
-        <v>5.7634475073812703E-2</v>
+        <v>7.6089067248938796E-2</v>
       </c>
       <c r="E3">
-        <v>8.4489184046263696E-2</v>
+        <v>9.7246725299768202E-2</v>
       </c>
       <c r="F3">
-        <v>14.9567766189575</v>
+        <v>19.1255283355713</v>
       </c>
       <c r="G3">
-        <v>10.094454665147399</v>
+        <v>12.208550671805501</v>
       </c>
       <c r="H3">
-        <v>15.139180464672</v>
+        <v>19.475242929230301</v>
       </c>
       <c r="I3">
-        <v>20.866480709777999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>24.9188048990681</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.1644E-2</v>
+        <v>4.2008999999999998E-2</v>
       </c>
       <c r="C4">
-        <v>7.0646895091496902E-3</v>
+        <v>3.5742177755241203E-2</v>
       </c>
       <c r="D4">
-        <v>1.23730661044278E-2</v>
+        <v>4.1543346781135998E-2</v>
       </c>
       <c r="E4">
-        <v>1.6981220942902001E-2</v>
+        <v>4.8778110229772298E-2</v>
       </c>
       <c r="F4">
-        <v>8.6053009033203107</v>
+        <v>27.572746276855501</v>
       </c>
       <c r="G4">
-        <v>4.4228430578178397</v>
+        <v>23.103145919498701</v>
       </c>
       <c r="H4">
-        <v>7.9943263962908997</v>
+        <v>27.163937425294701</v>
       </c>
       <c r="I4">
-        <v>11.0258806653991</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>32.069287244517199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.1638000000000001E-2</v>
+        <v>7.2021000000000002E-2</v>
       </c>
       <c r="C5">
-        <v>5.9796201907664796E-3</v>
+        <v>6.1227130076573898E-2</v>
       </c>
       <c r="D5">
-        <v>1.33345329694592E-2</v>
+        <v>6.9352140941810997E-2</v>
       </c>
       <c r="E5">
-        <v>2.3325951486200199E-2</v>
+        <v>7.9789485527358206E-2</v>
       </c>
       <c r="F5">
-        <v>6.2886328697204599</v>
+        <v>32.731925964355497</v>
       </c>
       <c r="G5">
-        <v>2.4174549488912298</v>
+        <v>27.460226538189399</v>
       </c>
       <c r="H5">
-        <v>5.9941095820992603</v>
+        <v>31.641434330748702</v>
       </c>
       <c r="I5">
-        <v>10.908317892086799</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>35.727308679751999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>8.0854999999999996E-2</v>
+        <v>0.16683000000000001</v>
       </c>
       <c r="C6">
-        <v>4.9565943848731898E-2</v>
+        <v>0.107747108303553</v>
       </c>
       <c r="D6">
-        <v>8.8740345047572902E-2</v>
+        <v>0.16501369497752499</v>
       </c>
       <c r="E6">
-        <v>0.142101271856167</v>
+        <v>0.205648955168415</v>
       </c>
       <c r="F6">
-        <v>14.9223022460938</v>
+        <v>28.001768112182599</v>
       </c>
       <c r="G6">
-        <v>8.2868867755988909</v>
+        <v>16.271478470030601</v>
       </c>
       <c r="H6">
-        <v>14.8005521337343</v>
+        <v>27.566282682777899</v>
       </c>
       <c r="I6">
-        <v>23.1344656214103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>35.893128041847298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5.1524000000000003E-4</v>
+        <v>2.1256000000000001E-2</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1.24042775031866E-2</v>
       </c>
       <c r="D7">
-        <v>1.5050174671645501E-3</v>
+        <v>1.9142234930979201E-2</v>
       </c>
       <c r="E7">
-        <v>6.2498169861112899E-3</v>
+        <v>2.6511395884647002E-2</v>
       </c>
       <c r="F7">
-        <v>2.1348814964294398</v>
+        <v>55.430652618408203</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>30.496920512152801</v>
       </c>
       <c r="H7">
-        <v>4.0620131081039004</v>
+        <v>49.378587010639599</v>
       </c>
       <c r="I7">
-        <v>19.022444351207302</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>58.987221325710898</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>3.5757999999999998E-2</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2.73242244312847E-2</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>3.5020475189575302E-2</v>
       </c>
       <c r="E8">
-        <v>2.2209150448466498E-3</v>
+        <v>4.50718440484578E-2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>39.084800720214801</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>30.1175061227678</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>38.101802529896801</v>
       </c>
       <c r="I8">
-        <v>2.6714807032385801</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>47.3622596304307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1.4308E-2</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1.12359463506059E-2</v>
       </c>
       <c r="D9">
-        <v>1.15240375608489E-4</v>
+        <v>1.40462191617948E-2</v>
       </c>
       <c r="E9">
-        <v>1.2581761072087501E-3</v>
+        <v>1.7555745587779201E-2</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>33.646373748779297</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>25.7546206233969</v>
       </c>
       <c r="H9">
-        <v>0.27009327869275701</v>
+        <v>32.552094012584902</v>
       </c>
       <c r="I9">
-        <v>2.9797053652013599</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>40.858824465191603</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>4.0836999999999998E-2</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>2.91621797375082E-2</v>
       </c>
       <c r="D10">
-        <v>1.2958086254006901E-3</v>
+        <v>3.8851697216037699E-2</v>
       </c>
       <c r="E10">
-        <v>4.7982044245204599E-3</v>
+        <v>4.9829809885687998E-2</v>
       </c>
       <c r="F10">
-        <v>0.14643286168575301</v>
+        <v>34.886669158935497</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>24.408244971397899</v>
       </c>
       <c r="H10">
-        <v>1.12038310889118</v>
+        <v>32.889460783243301</v>
       </c>
       <c r="I10">
-        <v>4.3491114840202396</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>42.068106255548997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4.4118999999999998E-2</v>
+        <v>4.8224000000000001E-3</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>3.4259692751823202E-2</v>
+        <v>1.0853433400494101E-2</v>
       </c>
       <c r="E11">
-        <v>6.3571712346756501E-2</v>
+        <v>4.7566344986095202E-2</v>
       </c>
       <c r="F11">
-        <v>15.6389722824097</v>
+        <v>1.80223441123962</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>12.218065735973999</v>
+        <v>4.0651668469694098</v>
       </c>
       <c r="I11">
-        <v>21.698495469767401</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18.063023966803701</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>6.5021999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1.44053005115209E-2</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>6.1521358586831602E-2</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>7.7610762382393395E-2</v>
+        <v>2.6790134692621599E-2</v>
       </c>
       <c r="F12">
-        <v>15.94287109375</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>3.4827521234791399</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>14.438559948014101</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>18.396810357055902</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6.1461505947079997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>4.2960000000000003E-3</v>
+        <v>3.9461999999999997E-2</v>
       </c>
       <c r="C13">
-        <v>1.17648298155671E-3</v>
+        <v>2.82401135941301E-2</v>
       </c>
       <c r="D13">
-        <v>6.10051924579867E-3</v>
+        <v>3.76850805280129E-2</v>
       </c>
       <c r="E13">
-        <v>1.5289768884975199E-2</v>
+        <v>4.80575476439365E-2</v>
       </c>
       <c r="F13">
-        <v>6.7652282714843803</v>
+        <v>52.121994018554702</v>
       </c>
       <c r="G13">
-        <v>1.32964673720199</v>
+        <v>36.591625308674402</v>
       </c>
       <c r="H13">
-        <v>7.9209960704686004</v>
+        <v>48.088153054772199</v>
       </c>
       <c r="I13">
-        <v>19.342256078009601</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>57.978759000894698</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>5.4406999999999997E-2</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>3.3202199670747501E-2</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>5.0973795259511699E-2</v>
       </c>
       <c r="E14">
-        <v>1.18241452306669E-2</v>
+        <v>7.2470667520223894E-2</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>52.308391571044901</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>34.521514464457901</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>48.851911814603</v>
       </c>
       <c r="I14">
-        <v>13.371213441618099</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>60.855884756151603</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>4.3123000000000002E-2</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>2.0104593892970399E-2</v>
       </c>
       <c r="D15">
-        <v>1.4788030110489099E-3</v>
+        <v>3.99252134826601E-2</v>
       </c>
       <c r="E15">
-        <v>1.13025850879378E-2</v>
+        <v>5.4825271486491099E-2</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>33.564174652099602</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>16.1191098272209</v>
       </c>
       <c r="H15">
-        <v>1.17436168439218</v>
+        <v>30.701711250860502</v>
       </c>
       <c r="I15">
-        <v>8.6632178220095408</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>43.459580743332701</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>7.9968999999999995E-3</v>
+        <v>2.0976999999999999E-2</v>
       </c>
       <c r="C16">
-        <v>4.6993762054879399E-3</v>
+        <v>1.3857590490339E-2</v>
       </c>
       <c r="D16">
-        <v>8.4661172905059097E-3</v>
+        <v>1.9854812351002699E-2</v>
       </c>
       <c r="E16">
-        <v>1.3296778656459E-2</v>
+        <v>2.63576649498065E-2</v>
       </c>
       <c r="F16">
-        <v>6.6620631217956499</v>
+        <v>18.791954040527301</v>
       </c>
       <c r="G16">
-        <v>4.3348690445624598</v>
+        <v>11.838584268264</v>
       </c>
       <c r="H16">
-        <v>7.7157692892978798</v>
+        <v>17.278788211247399</v>
       </c>
       <c r="I16">
-        <v>12.186621392696599</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>23.838473965231199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>3.4262000000000001E-2</v>
+        <v>1.6188000000000001E-2</v>
       </c>
       <c r="C17">
-        <v>1.6868445823103199E-2</v>
+        <v>1.1441554933391201E-2</v>
       </c>
       <c r="D17">
-        <v>3.2684446525940297E-2</v>
+        <v>1.8123249062833299E-2</v>
       </c>
       <c r="E17">
-        <v>4.0702816952716402E-2</v>
+        <v>2.5680449180722799E-2</v>
       </c>
       <c r="F17">
-        <v>13.2160987854004</v>
+        <v>6.5469498634338397</v>
       </c>
       <c r="G17">
-        <v>7.1289515550740896</v>
+        <v>4.2672479443101903</v>
       </c>
       <c r="H17">
-        <v>12.5902125652901</v>
+        <v>6.8540001001247299</v>
       </c>
       <c r="I17">
-        <v>15.4155468281811</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>10.0801482592922</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>6.7238999999999997E-3</v>
+        <v>3.8519999999999999E-2</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>2.3120592084282899E-2</v>
       </c>
       <c r="D18">
-        <v>8.8585015795957702E-3</v>
+        <v>3.6913463509545601E-2</v>
       </c>
       <c r="E18">
-        <v>1.6815463543000401E-2</v>
+        <v>5.5385526825291E-2</v>
       </c>
       <c r="F18">
-        <v>3.3844108581543</v>
+        <v>17.246515274047901</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>9.8313898875188706</v>
       </c>
       <c r="H18">
-        <v>3.9399053891258902</v>
+        <v>16.254247060007401</v>
       </c>
       <c r="I18">
-        <v>7.55092269198013</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>26.1377990643442</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>6.9099999999999995E-2</v>
+        <v>4.6163999999999997E-2</v>
       </c>
       <c r="C19">
-        <v>4.0782309289255497E-2</v>
+        <v>3.3102668237756101E-2</v>
       </c>
       <c r="D19">
-        <v>6.7012346576223306E-2</v>
+        <v>4.8966010879751401E-2</v>
       </c>
       <c r="E19">
-        <v>8.2793613051292694E-2</v>
+        <v>6.3832722486098101E-2</v>
       </c>
       <c r="F19">
-        <v>11.7542314529419</v>
+        <v>8.1537513732910192</v>
       </c>
       <c r="G19">
-        <v>7.4491789919519897</v>
+        <v>5.5533490176714997</v>
       </c>
       <c r="H19">
-        <v>11.5185813910024</v>
+        <v>8.2610011676753192</v>
       </c>
       <c r="I19">
-        <v>14.173277731417601</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11.2159190617544</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>8.1442000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>3.9936289426392997E-2</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>8.2839195312098393E-2</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0.116322444239451</v>
+        <v>2.34665684387752E-2</v>
       </c>
       <c r="F20">
-        <v>10.436448097229</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>5.2942990945300803</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>10.5656360021949</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>15.7535176932388</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2.7618044122942602</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.27651999999999999</v>
+        <v>4.4329E-2</v>
       </c>
       <c r="C21">
-        <v>0.20404383714329999</v>
+        <v>2.3658132043617702E-2</v>
       </c>
       <c r="D21">
-        <v>0.26652098278280401</v>
+        <v>6.7302376476896103E-2</v>
       </c>
       <c r="E21">
-        <v>0.321233448451547</v>
+        <v>0.125939655624528</v>
       </c>
       <c r="F21">
-        <v>13.635404586791999</v>
+        <v>2.5235321521759002</v>
       </c>
       <c r="G21">
-        <v>10.163225064827399</v>
+        <v>1.09344237299528</v>
       </c>
       <c r="H21">
-        <v>13.4636123470471</v>
+        <v>3.11202421122201</v>
       </c>
       <c r="I21">
-        <v>17.258041380380501</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>5.76206795855372</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>6.4865999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>1.10898609365841E-2</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>5.3966993958188998E-2</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>7.7387794286196201E-2</v>
+        <v>1.8611732237580701E-2</v>
       </c>
       <c r="F22">
-        <v>53.5085258483887</v>
+        <v>0.22666272521019001</v>
       </c>
       <c r="G22">
-        <v>9.7827477993070797</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>50.911186727895299</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>67.027805579493105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13.3847279075635</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1.0619E-2</v>
+        <v>0.10389</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>4.2489857480738198E-2</v>
       </c>
       <c r="D23">
-        <v>1.7827021236420201E-2</v>
+        <v>9.2739614840767398E-2</v>
       </c>
       <c r="E23">
-        <v>5.2127188313077E-2</v>
+        <v>0.153354975716439</v>
       </c>
       <c r="F23">
-        <v>1.1795871257782</v>
+        <v>16.8649597167969</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>6.7305660972841199</v>
       </c>
       <c r="H23">
-        <v>3.0909083130866102</v>
+        <v>14.9436934754916</v>
       </c>
       <c r="I23">
-        <v>8.7865048250748803</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>25.386791167089999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>4.4793999999999997E-3</v>
+        <v>3.9442999999999998E-4</v>
       </c>
       <c r="C24">
-        <v>2.0640948015161502E-3</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>4.1379814265193604E-3</v>
+        <v>4.7777593925154698E-4</v>
       </c>
       <c r="E24">
-        <v>5.86841984049692E-3</v>
+        <v>2.3432908685788499E-3</v>
       </c>
       <c r="F24">
-        <v>29.8222846984863</v>
+        <v>2.87548160552979</v>
       </c>
       <c r="G24">
-        <v>12.5018041319061</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>27.065386589166302</v>
+        <v>2.8655539893470299</v>
       </c>
       <c r="I24">
-        <v>39.683697548427503</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>14.5180283416985</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>8.1467131259040398E-2</v>
       </c>
       <c r="D25">
-        <v>6.1765929271771604E-3</v>
+        <v>0.113482151248066</v>
       </c>
       <c r="E25">
-        <v>7.3758776220578998E-2</v>
+        <v>0.14639225172451101</v>
       </c>
       <c r="F25">
-        <v>1.45115613937378</v>
+        <v>43.398204803466797</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>26.130722261464499</v>
       </c>
       <c r="H25">
-        <v>2.3063214157032101</v>
+        <v>43.665244291226998</v>
       </c>
       <c r="I25">
-        <v>25.430080995046001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>57.500386323853597</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>1.5165E-2</v>
+        <v>3.4762999999999999E-3</v>
       </c>
       <c r="C26">
-        <v>7.3631509594052997E-3</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1.4285390582310299E-2</v>
+        <v>2.4087060887728498E-3</v>
       </c>
       <c r="E26">
-        <v>2.5271993585200599E-2</v>
+        <v>6.1967319622095798E-3</v>
       </c>
       <c r="F26">
-        <v>72.525939941406307</v>
+        <v>19.8954887390137</v>
       </c>
       <c r="G26">
-        <v>49.573813164866699</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>74.480887920605497</v>
+        <v>10.767446530042999</v>
       </c>
       <c r="I26">
-        <v>87.282129480087093</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>33.624644257084903</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2.8614999999999999E-3</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>7.0573997534280003E-3</v>
       </c>
       <c r="E27">
-        <v>1.8244698504328801E-2</v>
+        <v>2.22011563486538E-2</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>3.3584139347076398</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>6.3821365213568297</v>
       </c>
       <c r="I27">
-        <v>14.059546454602099</v>
+        <v>20.022304758028401</v>
       </c>
     </row>
   </sheetData>
@@ -1308,11 +1334,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF62622D-9A9D-42EF-AC19-E803DACD700B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{461724D2-7A8D-4294-B04B-FE123235B1E1}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1341,708 +1367,708 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.51549999999999996</v>
+        <v>0.14985999999999999</v>
       </c>
       <c r="C2">
-        <v>0.38525355792820898</v>
+        <v>0.10016345266011201</v>
       </c>
       <c r="D2">
-        <v>0.49676771043099599</v>
+        <v>0.154134868290875</v>
       </c>
       <c r="E2">
-        <v>0.62609103925280296</v>
+        <v>0.21124434612463799</v>
       </c>
       <c r="F2">
-        <v>48.791473388671903</v>
+        <v>14.813480377197299</v>
       </c>
       <c r="G2">
-        <v>39.047071922376198</v>
+        <v>10.067914887212099</v>
       </c>
       <c r="H2">
-        <v>48.7777126330082</v>
+        <v>14.9209318948326</v>
       </c>
       <c r="I2">
-        <v>56.941437568574798</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>20.935862711278901</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.14882000000000001</v>
+        <v>1.1495E-2</v>
       </c>
       <c r="C3">
-        <v>0.102258296878218</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0.13535783691908301</v>
+        <v>1.31588818800931E-2</v>
       </c>
       <c r="E3">
-        <v>0.178329207652282</v>
+        <v>2.5603702331973201E-2</v>
       </c>
       <c r="F3">
-        <v>35.645050048828097</v>
+        <v>3.43089771270752</v>
       </c>
       <c r="G3">
-        <v>27.8854146848258</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>34.991800291798199</v>
+        <v>3.3964055012077501</v>
       </c>
       <c r="I3">
-        <v>42.640940592266901</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6.3492813135272703</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>7.8509999999999996E-2</v>
+        <v>1.8634999999999999E-2</v>
       </c>
       <c r="C4">
-        <v>5.8194511132566198E-2</v>
+        <v>1.4575341527967699E-2</v>
       </c>
       <c r="D4">
-        <v>7.5954359341010899E-2</v>
+        <v>1.9217903145679699E-2</v>
       </c>
       <c r="E4">
-        <v>9.7020737577643595E-2</v>
+        <v>2.5004728431401502E-2</v>
       </c>
       <c r="F4">
-        <v>49.125007629394503</v>
+        <v>12.249279975891101</v>
       </c>
       <c r="G4">
-        <v>39.3646465338173</v>
+        <v>9.3968101713147494</v>
       </c>
       <c r="H4">
-        <v>49.4382194667539</v>
+        <v>12.440306963997299</v>
       </c>
       <c r="I4">
-        <v>57.6230063658587</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16.712822204867901</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.10181999999999999</v>
+        <v>3.4728000000000002E-2</v>
       </c>
       <c r="C5">
-        <v>7.1846407086820302E-2</v>
+        <v>2.14419417356762E-2</v>
       </c>
       <c r="D5">
-        <v>9.9768028138051898E-2</v>
+        <v>3.4626763076063001E-2</v>
       </c>
       <c r="E5">
-        <v>0.13113338538920599</v>
+        <v>5.1887748768880602E-2</v>
       </c>
       <c r="F5">
-        <v>44.381629943847699</v>
+        <v>15.6225776672363</v>
       </c>
       <c r="G5">
-        <v>33.610609387703398</v>
+        <v>9.8079264480923207</v>
       </c>
       <c r="H5">
-        <v>45.294185739103099</v>
+        <v>15.6197601387773</v>
       </c>
       <c r="I5">
-        <v>54.633131867790503</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>24.0319515767548</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.27982000000000001</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.20029122450217601</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0.26876800106889198</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.329176832769428</v>
+        <v>2.3321317476647199E-2</v>
       </c>
       <c r="F6">
-        <v>43.938545227050803</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>35.4797825127389</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>44.023541744622797</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>51.654711860472503</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3.4897067199381899</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>4.3166999999999997E-3</v>
+        <v>8.1436000000000008E-3</v>
       </c>
       <c r="C7">
-        <v>4.3257983190606502E-4</v>
+        <v>2.9879052766780601E-3</v>
       </c>
       <c r="D7">
-        <v>3.6900985408786298E-3</v>
+        <v>7.5382121042336797E-3</v>
       </c>
       <c r="E7">
-        <v>1.74442686944172E-2</v>
+        <v>1.4220572532387701E-2</v>
       </c>
       <c r="F7">
-        <v>9.8535394668579102</v>
+        <v>21.2289123535156</v>
       </c>
       <c r="G7">
-        <v>1.2354100156999801</v>
+        <v>7.2416093696884296</v>
       </c>
       <c r="H7">
-        <v>9.8313167048693799</v>
+        <v>19.013277833429701</v>
       </c>
       <c r="I7">
-        <v>40.730821624428501</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>32.440461121817101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>3.5396999999999998E-2</v>
+        <v>2.3441E-2</v>
       </c>
       <c r="C8">
-        <v>2.29249344568935E-2</v>
+        <v>1.4645706781991201E-2</v>
       </c>
       <c r="D8">
-        <v>3.5970270913894098E-2</v>
+        <v>2.2423335524703401E-2</v>
       </c>
       <c r="E8">
-        <v>5.5449614013515898E-2</v>
+        <v>2.9912148266448099E-2</v>
       </c>
       <c r="F8">
-        <v>38.060176849365199</v>
+        <v>24.689191818237301</v>
       </c>
       <c r="G8">
-        <v>25.070479909159801</v>
+        <v>16.143170890142201</v>
       </c>
       <c r="H8">
-        <v>39.869524640029901</v>
+        <v>24.2600783095704</v>
       </c>
       <c r="I8">
-        <v>53.056728665384597</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>33.649660837823497</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.7179E-2</v>
+        <v>1.2367E-2</v>
       </c>
       <c r="C9">
-        <v>1.19345149343788E-2</v>
+        <v>9.1991169078180692E-3</v>
       </c>
       <c r="D9">
-        <v>1.7317452788037702E-2</v>
+        <v>1.2002739685412401E-2</v>
       </c>
       <c r="E9">
-        <v>2.7879179759850801E-2</v>
+        <v>1.44175434975273E-2</v>
       </c>
       <c r="F9">
-        <v>39.658523559570298</v>
+        <v>27.975894927978501</v>
       </c>
       <c r="G9">
-        <v>29.883059087239101</v>
+        <v>21.505061319834901</v>
       </c>
       <c r="H9">
-        <v>40.872492614324798</v>
+        <v>27.785138934365801</v>
       </c>
       <c r="I9">
-        <v>54.589380390424203</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>34.875309958621301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>3.5765999999999999E-2</v>
+        <v>4.233E-2</v>
       </c>
       <c r="C10">
-        <v>2.2814913703058801E-2</v>
+        <v>3.08700011451409E-2</v>
       </c>
       <c r="D10">
-        <v>3.6769523272159002E-2</v>
+        <v>4.1079059346395601E-2</v>
       </c>
       <c r="E10">
-        <v>6.7788629799559699E-2</v>
+        <v>5.0229439631711698E-2</v>
       </c>
       <c r="F10">
-        <v>30.694133758544901</v>
+        <v>35.024604797363303</v>
       </c>
       <c r="G10">
-        <v>20.690888488617599</v>
+        <v>26.344010082760501</v>
       </c>
       <c r="H10">
-        <v>32.167607411619002</v>
+        <v>34.394985444823902</v>
       </c>
       <c r="I10">
-        <v>49.785746358559201</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>43.3112630390251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.15623999999999999</v>
+        <v>6.9775000000000004E-2</v>
       </c>
       <c r="C11">
-        <v>0.108749992658313</v>
+        <v>3.76247627143909E-2</v>
       </c>
       <c r="D11">
-        <v>0.146513377769873</v>
+        <v>6.9115178576722405E-2</v>
       </c>
       <c r="E11">
-        <v>0.18483399586133201</v>
+        <v>7.7734095528100899E-2</v>
       </c>
       <c r="F11">
-        <v>53.826690673828097</v>
+        <v>24.665889739990199</v>
       </c>
       <c r="G11">
-        <v>40.817455831142802</v>
+        <v>14.350560993858901</v>
       </c>
       <c r="H11">
-        <v>52.081283084944502</v>
+        <v>24.393908561071999</v>
       </c>
       <c r="I11">
-        <v>64.477111401554296</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>27.730538290822299</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.24868000000000001</v>
+        <v>8.4320000000000006E-2</v>
       </c>
       <c r="C12">
-        <v>0.21488335229156</v>
+        <v>6.9487733893760395E-2</v>
       </c>
       <c r="D12">
-        <v>0.234023148919309</v>
+        <v>8.45630323249493E-2</v>
       </c>
       <c r="E12">
-        <v>0.26321570532400002</v>
+        <v>0.10111935835767399</v>
       </c>
       <c r="F12">
-        <v>56.444019317627003</v>
+        <v>20.110898971557599</v>
       </c>
       <c r="G12">
-        <v>51.536438439994399</v>
+        <v>15.718500746116</v>
       </c>
       <c r="H12">
-        <v>55.261251960597399</v>
+        <v>19.730138313711802</v>
       </c>
       <c r="I12">
-        <v>61.161273118122502</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>24.877377736140499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.7696E-2</v>
+        <v>1.2440000000000001E-3</v>
       </c>
       <c r="C13">
-        <v>6.0421473020726005E-4</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1.36553666353565E-2</v>
+        <v>1.04050217185007E-3</v>
       </c>
       <c r="E13">
-        <v>2.2783384436505998E-2</v>
+        <v>3.1590296752418499E-2</v>
       </c>
       <c r="F13">
-        <v>24.091417312622099</v>
+        <v>1.4498751163482699</v>
       </c>
       <c r="G13">
-        <v>0.71505471921683605</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>18.600838564844501</v>
+        <v>1.3998909266810899</v>
       </c>
       <c r="I13">
-        <v>29.741294383830901</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>32.5216523892555</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>7.7010000000000004E-3</v>
+        <v>2.6450000000000001E-2</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1.56762762256684E-2</v>
       </c>
       <c r="D14">
-        <v>1.15115898346066E-2</v>
+        <v>2.41423993766746E-2</v>
       </c>
       <c r="E14">
-        <v>3.5042058914002402E-2</v>
+        <v>5.3274493327095197E-2</v>
       </c>
       <c r="F14">
-        <v>10.529666900634799</v>
+        <v>23.128421783447301</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>15.7442953148439</v>
       </c>
       <c r="H14">
-        <v>11.564495890600201</v>
+        <v>24.453295906754501</v>
       </c>
       <c r="I14">
-        <v>30.0717750282944</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>43.923087526341398</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>7.8543000000000002E-2</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>5.1664011788926899E-2</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>7.8252667132656203E-2</v>
       </c>
       <c r="E15">
-        <v>8.08979946947741E-3</v>
+        <v>9.8233791109409996E-2</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>59.481922149658203</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>42.9456861850406</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>60.5641152383443</v>
       </c>
       <c r="I15">
-        <v>6.2377807221521504</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>71.965889650559205</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.1899999999999999E-2</v>
+        <v>5.2142000000000001E-2</v>
       </c>
       <c r="C16">
-        <v>1.47928224637242E-2</v>
+        <v>4.32530584812717E-2</v>
       </c>
       <c r="D16">
-        <v>2.2595294115509298E-2</v>
+        <v>5.0872008838790499E-2</v>
       </c>
       <c r="E16">
-        <v>2.9420374110375399E-2</v>
+        <v>6.17218178508799E-2</v>
       </c>
       <c r="F16">
-        <v>19.6372470855713</v>
+        <v>44.765583038330099</v>
       </c>
       <c r="G16">
-        <v>13.9404196400363</v>
+        <v>38.951718936690099</v>
       </c>
       <c r="H16">
-        <v>20.737570532467799</v>
+        <v>44.542123201644202</v>
       </c>
       <c r="I16">
-        <v>26.509974302314799</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>50.782738253135598</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.11360000000000001</v>
+        <v>8.3049999999999999E-2</v>
       </c>
       <c r="C17">
-        <v>0.100282650269509</v>
+        <v>6.9841038279331996E-2</v>
       </c>
       <c r="D17">
-        <v>0.109118988521514</v>
+        <v>8.2768314801538095E-2</v>
       </c>
       <c r="E17">
-        <v>0.127455339963057</v>
+        <v>8.8992032127020504E-2</v>
       </c>
       <c r="F17">
-        <v>42.361747741699197</v>
+        <v>31.4079685211182</v>
       </c>
       <c r="G17">
-        <v>39.630982559636401</v>
+        <v>27.806988299459199</v>
       </c>
       <c r="H17">
-        <v>42.316503181253097</v>
+        <v>31.169138949463999</v>
       </c>
       <c r="I17">
-        <v>48.6141160426086</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>33.528629462151898</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>6.6932000000000005E-2</v>
+        <v>0.10982</v>
       </c>
       <c r="C18">
-        <v>5.3457007377027597E-2</v>
+        <v>8.3978519901184795E-2</v>
       </c>
       <c r="D18">
-        <v>6.8712012510648998E-2</v>
+        <v>0.10719003872383299</v>
       </c>
       <c r="E18">
-        <v>0.105499159991241</v>
+        <v>0.121405021729208</v>
       </c>
       <c r="F18">
-        <v>30.491893768310501</v>
+        <v>47.717281341552699</v>
       </c>
       <c r="G18">
-        <v>25.7125060144275</v>
+        <v>40.958445927678497</v>
       </c>
       <c r="H18">
-        <v>31.903987857804299</v>
+        <v>47.099107678542701</v>
       </c>
       <c r="I18">
-        <v>43.808803961604099</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>51.5893668675334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.22078</v>
+        <v>0.21101</v>
       </c>
       <c r="C19">
-        <v>0.193168261565415</v>
+        <v>0.18179704301188701</v>
       </c>
       <c r="D19">
-        <v>0.214502882389217</v>
+        <v>0.20928987989234299</v>
       </c>
       <c r="E19">
-        <v>0.239497223246396</v>
+        <v>0.223628742980755</v>
       </c>
       <c r="F19">
-        <v>36.833255767822301</v>
+        <v>35.238025665283203</v>
       </c>
       <c r="G19">
-        <v>34.300209675260703</v>
+        <v>31.8633098223481</v>
       </c>
       <c r="H19">
-        <v>37.208738158012302</v>
+        <v>35.010397612783301</v>
       </c>
       <c r="I19">
-        <v>41.172499574040202</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>37.026350970609798</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.25939000000000001</v>
+        <v>0.30753999999999998</v>
       </c>
       <c r="C20">
-        <v>0.163114424978199</v>
+        <v>0.28031245534157501</v>
       </c>
       <c r="D20">
-        <v>0.24746738021835499</v>
+        <v>0.30485772465946698</v>
       </c>
       <c r="E20">
-        <v>0.30857713423944499</v>
+        <v>0.33846907530952097</v>
       </c>
       <c r="F20">
-        <v>32.225711822509801</v>
+        <v>37.332191467285199</v>
       </c>
       <c r="G20">
-        <v>21.855548622179501</v>
+        <v>33.242521659161198</v>
       </c>
       <c r="H20">
-        <v>31.687075383654498</v>
+        <v>37.345581899636102</v>
       </c>
       <c r="I20">
-        <v>38.859768059949303</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>41.971237422140902</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.72780999999999996</v>
+        <v>0.66418999999999995</v>
       </c>
       <c r="C21">
-        <v>0.45743521077365301</v>
+        <v>0.59606255923903695</v>
       </c>
       <c r="D21">
-        <v>0.67448901331498001</v>
+        <v>0.665133725375603</v>
       </c>
       <c r="E21">
-        <v>0.81206181365402197</v>
+        <v>0.75115808618192503</v>
       </c>
       <c r="F21">
-        <v>34.725612640380902</v>
+        <v>30.7431240081787</v>
       </c>
       <c r="G21">
-        <v>24.258457449629599</v>
+        <v>27.340302767300599</v>
       </c>
       <c r="H21">
-        <v>33.933314037881203</v>
+        <v>30.790036328409599</v>
       </c>
       <c r="I21">
-        <v>40.126198249506899</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>35.136710163694303</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>3.4640999999999998E-2</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>2.30712852633169E-2</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>3.3540310192077899E-2</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>5.8666877016104603E-2</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>23.9769992828369</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>16.3838497811123</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>22.944844937182001</v>
       </c>
       <c r="I22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>34.866628462103399</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>6.4810000000000006E-2</v>
+        <v>0.38179000000000002</v>
       </c>
       <c r="C23">
-        <v>1.2755584448084899E-2</v>
+        <v>0.29410120842194398</v>
       </c>
       <c r="D23">
-        <v>7.0313029520037998E-2</v>
+        <v>0.37109112779144898</v>
       </c>
       <c r="E23">
-        <v>0.12256850333743</v>
+        <v>0.40189613519602102</v>
       </c>
       <c r="F23">
-        <v>11.4463844299316</v>
+        <v>59.735805511474602</v>
       </c>
       <c r="G23">
-        <v>2.49055583490648</v>
+        <v>52.722059362361698</v>
       </c>
       <c r="H23">
-        <v>12.1734053348555</v>
+        <v>59.213674338428497</v>
       </c>
       <c r="I23">
-        <v>20.142756424299499</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>63.202793583536597</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>7.7882000000000003E-3</v>
+        <v>9.1301999999999996E-4</v>
       </c>
       <c r="C24">
-        <v>3.7985692840118699E-3</v>
+        <v>2.04886555116665E-4</v>
       </c>
       <c r="D24">
-        <v>7.0409667780372102E-3</v>
+        <v>1.0365729964961199E-3</v>
       </c>
       <c r="E24">
-        <v>1.12448810507229E-2</v>
+        <v>2.1715561260599999E-3</v>
       </c>
       <c r="F24">
-        <v>45.333633422851598</v>
+        <v>6.7870597839355504</v>
       </c>
       <c r="G24">
-        <v>28.229140589209301</v>
+        <v>1.1520754790787799</v>
       </c>
       <c r="H24">
-        <v>45.423382536235799</v>
+        <v>6.4946760058391098</v>
       </c>
       <c r="I24">
-        <v>64.228959141938901</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12.9911062947654</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>8.5428000000000001E-4</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>7.4809189303632804E-4</v>
       </c>
       <c r="E25">
-        <v>1.3416097195695399E-2</v>
+        <v>3.1996224192465698E-3</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>0.32487452030181901</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>0.28589754886648699</v>
       </c>
       <c r="I25">
-        <v>4.2299349514249203</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1.2696350479068099</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2.3541E-4</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -2051,10 +2077,10 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>3.5817060031762102E-3</v>
+        <v>4.6929459388900301E-4</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1.7829298973083501</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -2063,36 +2089,36 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>14.1867540595888</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2.5802995570884</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>1.0352999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>9.0412469789796501E-3</v>
+        <v>3.1736010671915298E-4</v>
       </c>
       <c r="E27">
-        <v>1.59418569236979E-2</v>
+        <v>3.1402083782528902E-3</v>
       </c>
       <c r="F27">
-        <v>7.8996872901916504</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>7.5085440593642998</v>
+        <v>0.24058496774667601</v>
       </c>
       <c r="I27">
-        <v>11.6162028571742</v>
+        <v>2.3799094976417399</v>
       </c>
     </row>
   </sheetData>
@@ -2101,11 +2127,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF89F2E8-373F-4511-BF74-91A0F915D4D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1FEC3B-7305-4647-BABE-4DD44CA22496}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2134,181 +2160,181 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.2397E-2</v>
+        <v>1.7788000000000002E-2</v>
       </c>
       <c r="C2">
-        <v>3.1666499728329502E-2</v>
+        <v>1.4826727138037499E-2</v>
       </c>
       <c r="D2">
-        <v>6.5971134548731894E-2</v>
+        <v>5.4469681040830498E-2</v>
       </c>
       <c r="E2">
-        <v>9.6606177719308003E-2</v>
+        <v>8.2218739746002106E-2</v>
       </c>
       <c r="F2">
-        <v>4.2524380683898899</v>
+        <v>2.1910643577575701</v>
       </c>
       <c r="G2">
-        <v>3.0535902294729298</v>
+        <v>1.46987322127794</v>
       </c>
       <c r="H2">
-        <v>6.4226150458762703</v>
+        <v>5.3305393781408501</v>
       </c>
       <c r="I2">
-        <v>9.7821159393196702</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>8.1221584357577896</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.10117</v>
+        <v>9.3227000000000004E-2</v>
       </c>
       <c r="C3">
-        <v>8.6259605991743801E-2</v>
+        <v>7.7422402149428304E-2</v>
       </c>
       <c r="D3">
-        <v>0.10179112445977199</v>
+        <v>8.9677141392463897E-2</v>
       </c>
       <c r="E3">
-        <v>0.11923720562231099</v>
+        <v>0.106946293184458</v>
       </c>
       <c r="F3">
-        <v>27.2506923675537</v>
+        <v>24.486242294311499</v>
       </c>
       <c r="G3">
-        <v>22.138274640241399</v>
+        <v>19.901628597170401</v>
       </c>
       <c r="H3">
-        <v>26.395881778265</v>
+        <v>22.958860688379598</v>
       </c>
       <c r="I3">
-        <v>30.9332554968769</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>26.8779644895953</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.9157999999999997E-3</v>
+        <v>3.2680000000000001E-3</v>
       </c>
       <c r="C4">
-        <v>4.5622160276187797E-3</v>
+        <v>2.1450416884850401E-3</v>
       </c>
       <c r="D4">
-        <v>9.9646462960908105E-3</v>
+        <v>8.6776596759335807E-3</v>
       </c>
       <c r="E4">
-        <v>1.50574138377512E-2</v>
+        <v>1.31519830034306E-2</v>
       </c>
       <c r="F4">
-        <v>4.5270256996154803</v>
+        <v>2.51812791824341</v>
       </c>
       <c r="G4">
-        <v>2.9623043400092701</v>
+        <v>1.3624031347506</v>
       </c>
       <c r="H4">
-        <v>6.3789143809228497</v>
+        <v>5.6188243845289403</v>
       </c>
       <c r="I4">
-        <v>9.7225760194330704</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>8.5735742204257903</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3.4954000000000001E-3</v>
+        <v>2.8429000000000002E-3</v>
       </c>
       <c r="C5">
-        <v>4.4218314458844997E-3</v>
+        <v>2.3357800601225302E-3</v>
       </c>
       <c r="D5">
-        <v>1.0372867741360601E-2</v>
+        <v>8.5977909972506702E-3</v>
       </c>
       <c r="E5">
-        <v>1.8879846288367301E-2</v>
+        <v>1.5512113572628701E-2</v>
       </c>
       <c r="F5">
-        <v>3.1783518791198699</v>
+        <v>1.64333379268646</v>
       </c>
       <c r="G5">
-        <v>1.9386213000797601</v>
+        <v>1.0294393229276799</v>
       </c>
       <c r="H5">
-        <v>4.6869048961077198</v>
+        <v>3.9602856314346302</v>
       </c>
       <c r="I5">
-        <v>8.5552279552015094</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>7.0622775916316201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6.8673999999999999E-2</v>
+        <v>5.7181000000000003E-2</v>
       </c>
       <c r="C6">
-        <v>6.0072435144606598E-2</v>
+        <v>4.9334153410666597E-2</v>
       </c>
       <c r="D6">
-        <v>8.4021986486095407E-2</v>
+        <v>7.2467065642694103E-2</v>
       </c>
       <c r="E6">
-        <v>0.10576204870364</v>
+        <v>9.1641895746959204E-2</v>
       </c>
       <c r="F6">
-        <v>13.012371063232401</v>
+        <v>9.8026046752929705</v>
       </c>
       <c r="G6">
-        <v>9.8520471064486905</v>
+        <v>8.0190934875790401</v>
       </c>
       <c r="H6">
-        <v>13.7259408870638</v>
+        <v>11.752116301518599</v>
       </c>
       <c r="I6">
-        <v>17.9293987547622</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15.3242432319462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>4.7153999999999998E-3</v>
+        <v>4.058E-3</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>3.39537504431157E-3</v>
+        <v>2.2321876234644598E-3</v>
       </c>
       <c r="E7">
-        <v>6.1828653661892699E-3</v>
+        <v>5.7730190604051504E-3</v>
       </c>
       <c r="F7">
-        <v>11.774359703064</v>
+        <v>10.9411973953247</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.4176051158479606</v>
+        <v>5.3936813807360497</v>
       </c>
       <c r="I7">
-        <v>17.3701836541074</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15.3344373977435</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2319,25 +2345,25 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1.6654822184527501E-3</v>
+        <v>1.3128671377419601E-3</v>
       </c>
       <c r="E8">
-        <v>6.3563124018450202E-3</v>
+        <v>5.0473929488978799E-3</v>
       </c>
       <c r="F8">
-        <v>0.80497372150421098</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1.8010929442653001</v>
+        <v>1.41996686952176</v>
       </c>
       <c r="I8">
-        <v>6.6554858087833901</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>5.3077868955735203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2345,28 +2371,28 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1.4278193357523701E-6</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>8.2091852933201205E-4</v>
+        <v>6.1087107342125196E-4</v>
       </c>
       <c r="E9">
-        <v>2.5528920069341201E-3</v>
+        <v>1.92909504561727E-3</v>
       </c>
       <c r="F9">
-        <v>0.99143975973129295</v>
+        <v>0.183493956923485</v>
       </c>
       <c r="G9">
-        <v>3.09709151487656E-3</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>1.92071894161654</v>
+        <v>1.43101150657108</v>
       </c>
       <c r="I9">
-        <v>5.98195199475298</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>4.3865135279888499</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2377,228 +2403,228 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>6.8496864097992798E-4</v>
+        <v>4.7557744243577099E-4</v>
       </c>
       <c r="E10">
-        <v>5.4044814172902996E-3</v>
+        <v>3.8694066844688398E-3</v>
       </c>
       <c r="F10">
-        <v>0.63257551193237305</v>
+        <v>0.302094876766205</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0.568358760982973</v>
+        <v>0.40712779464749699</v>
       </c>
       <c r="I10">
-        <v>4.7231672987716697</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3.3050997621347999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>3.7163000000000001E-3</v>
+        <v>3.4808E-3</v>
       </c>
       <c r="C11">
-        <v>7.8784300600746003E-4</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1.8803005589516902E-2</v>
+        <v>1.6576823096817801E-2</v>
       </c>
       <c r="E11">
-        <v>3.33972512555736E-2</v>
+        <v>3.0715937229705399E-2</v>
       </c>
       <c r="F11">
-        <v>4.0046024322509801</v>
+        <v>1.7186236381530799</v>
       </c>
       <c r="G11">
-        <v>0.333539130253933</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>6.7154932022027003</v>
+        <v>5.9935669648071004</v>
       </c>
       <c r="I11">
-        <v>12.349300798327301</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11.151286216633199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.325E-2</v>
+        <v>2.0553999999999999E-2</v>
       </c>
       <c r="C12">
-        <v>1.6796458769242299E-2</v>
+        <v>1.40822925402145E-2</v>
       </c>
       <c r="D12">
-        <v>4.8471739061205298E-2</v>
+        <v>4.2575006438859697E-2</v>
       </c>
       <c r="E12">
-        <v>6.2769670091952307E-2</v>
+        <v>5.6255397384596798E-2</v>
       </c>
       <c r="F12">
-        <v>8.4443845748901403</v>
+        <v>5.4284100532531703</v>
       </c>
       <c r="G12">
-        <v>4.1096301826495303</v>
+        <v>3.27566375847189</v>
       </c>
       <c r="H12">
-        <v>11.175957506806499</v>
+        <v>9.7345476815118008</v>
       </c>
       <c r="I12">
-        <v>14.675422459621499</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13.464816207028299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.2220999999999999E-2</v>
+        <v>1.0638E-2</v>
       </c>
       <c r="C13">
-        <v>2.9425816913972798E-4</v>
+        <v>2.6141872696734E-3</v>
       </c>
       <c r="D13">
-        <v>9.9860753531430708E-3</v>
+        <v>9.3779969811322601E-3</v>
       </c>
       <c r="E13">
-        <v>1.5938883626756401E-2</v>
+        <v>1.42473002615845E-2</v>
       </c>
       <c r="F13">
-        <v>15.784258842468301</v>
+        <v>14.174822807311999</v>
       </c>
       <c r="G13">
-        <v>0.32329719200770102</v>
+        <v>2.9465067263084102</v>
       </c>
       <c r="H13">
-        <v>13.726658653490199</v>
+        <v>12.102288286894</v>
       </c>
       <c r="I13">
-        <v>21.969370047149201</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18.9761837103222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.0959999999999999E-2</v>
+        <v>1.2338E-2</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>6.8321838925257099E-3</v>
+        <v>8.9384279456321703E-3</v>
       </c>
       <c r="E14">
-        <v>1.5046949740327199E-2</v>
+        <v>1.55858250598239E-2</v>
       </c>
       <c r="F14">
-        <v>9.6391267776489293</v>
+        <v>11.9531354904175</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>6.5121147842213398</v>
+        <v>8.6866971662097701</v>
       </c>
       <c r="I14">
-        <v>14.6802739107035</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15.5617279222066</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>8.1621000000000003E-3</v>
+        <v>8.711E-3</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1.5168410974962499E-3</v>
+        <v>1.0797323291863699E-3</v>
       </c>
       <c r="E15">
-        <v>1.23193783470349E-2</v>
+        <v>1.31541806771358E-2</v>
       </c>
       <c r="F15">
-        <v>5.3330559730529803</v>
+        <v>6.9539051055908203</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>1.2709785496981101</v>
+        <v>0.81713819611392102</v>
       </c>
       <c r="I15">
-        <v>9.7176013682742894</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>10.290586830855499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>8.4168000000000003E-3</v>
+        <v>8.1490999999999994E-3</v>
       </c>
       <c r="C16">
-        <v>4.0668066749680902E-3</v>
+        <v>2.5639814256367701E-3</v>
       </c>
       <c r="D16">
-        <v>6.93396635080321E-3</v>
+        <v>6.3323970680713802E-3</v>
       </c>
       <c r="E16">
-        <v>1.0085708542774E-2</v>
+        <v>1.0638032954393299E-2</v>
       </c>
       <c r="F16">
-        <v>7.6727046966552699</v>
+        <v>7.4613366127014196</v>
       </c>
       <c r="G16">
-        <v>3.7282489613068699</v>
+        <v>2.2170893409480001</v>
       </c>
       <c r="H16">
-        <v>6.3663715347834504</v>
+        <v>5.5547449778975704</v>
       </c>
       <c r="I16">
-        <v>9.1163078660800494</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>9.4305210489655895</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1.0796999999999999E-2</v>
+        <v>9.4062E-3</v>
       </c>
       <c r="C17">
-        <v>9.2277566112600896E-3</v>
+        <v>7.78863682279567E-3</v>
       </c>
       <c r="D17">
-        <v>1.92499118703859E-2</v>
+        <v>1.7267379181917199E-2</v>
       </c>
       <c r="E17">
-        <v>2.6808738700045898E-2</v>
+        <v>2.2415956090301802E-2</v>
       </c>
       <c r="F17">
-        <v>6.06664943695068</v>
+        <v>4.1147699356079102</v>
       </c>
       <c r="G17">
-        <v>3.77145182650519</v>
+        <v>2.9757533665118201</v>
       </c>
       <c r="H17">
-        <v>7.3998172635328503</v>
+        <v>6.4933602489371403</v>
       </c>
       <c r="I17">
-        <v>10.407101087916001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>8.7268142910058408</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2612,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>5.2548980312482497E-3</v>
+        <v>3.8726396881032998E-3</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2624,213 +2650,213 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>2.44976890922768</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1.8057906447577301</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>3.2735E-2</v>
+        <v>2.8761999999999999E-2</v>
       </c>
       <c r="C19">
-        <v>3.1255890909102101E-2</v>
+        <v>2.6623147610777598E-2</v>
       </c>
       <c r="D19">
-        <v>4.5283834865836002E-2</v>
+        <v>3.9603080480139302E-2</v>
       </c>
       <c r="E19">
-        <v>5.9015989568870802E-2</v>
+        <v>4.9829949561673498E-2</v>
       </c>
       <c r="F19">
-        <v>7.1160020828247097</v>
+        <v>5.3288946151733398</v>
       </c>
       <c r="G19">
-        <v>5.41818602327593</v>
+        <v>4.3996563734535403</v>
       </c>
       <c r="H19">
-        <v>7.7902091434913698</v>
+        <v>6.6709421630071999</v>
       </c>
       <c r="I19">
-        <v>10.2064963470338</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>8.4229085823339496</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.14288999999999999</v>
+        <v>0.13553000000000001</v>
       </c>
       <c r="C20">
-        <v>0.111985985581092</v>
+        <v>0.10685346682453301</v>
       </c>
       <c r="D20">
-        <v>0.14400003057285099</v>
+        <v>0.13158311948403001</v>
       </c>
       <c r="E20">
-        <v>0.16425011331481201</v>
+        <v>0.149683126706081</v>
       </c>
       <c r="F20">
-        <v>19.2619953155518</v>
+        <v>16.889762878418001</v>
       </c>
       <c r="G20">
-        <v>14.8111103087373</v>
+        <v>12.9075551847776</v>
       </c>
       <c r="H20">
-        <v>18.6351264264588</v>
+        <v>16.001308272043499</v>
       </c>
       <c r="I20">
-        <v>21.2414040110054</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18.5066713179997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.3246</v>
+        <v>0.27683999999999997</v>
       </c>
       <c r="C21">
-        <v>0.28652839918415701</v>
+        <v>0.23646182514893699</v>
       </c>
       <c r="D21">
-        <v>0.34200229157086598</v>
+        <v>0.28911931985476202</v>
       </c>
       <c r="E21">
-        <v>0.38136632601383902</v>
+        <v>0.32304371801828602</v>
       </c>
       <c r="F21">
-        <v>17.4806308746338</v>
+        <v>13.3336801528931</v>
       </c>
       <c r="G21">
-        <v>14.1926314071566</v>
+        <v>10.9968637437266</v>
       </c>
       <c r="H21">
-        <v>17.2703767634023</v>
+        <v>13.291533638767801</v>
       </c>
       <c r="I21">
-        <v>19.511500455810101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15.216919504651599</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1.593E-2</v>
+        <v>4.9152000000000001E-2</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>2.2620343694298401E-2</v>
       </c>
       <c r="D22">
-        <v>1.7479944530194601E-2</v>
+        <v>3.7851711701442602E-2</v>
       </c>
       <c r="E22">
-        <v>5.9294860612011099E-2</v>
+        <v>6.9154588648416601E-2</v>
       </c>
       <c r="F22">
-        <v>18.087659835815401</v>
+        <v>34.082267761230497</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>14.457766826024899</v>
       </c>
       <c r="H22">
-        <v>15.8907628534089</v>
+        <v>25.399771291842601</v>
       </c>
       <c r="I22">
-        <v>53.034414766187403</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>49.135579795094102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>4.3456000000000002E-2</v>
+        <v>3.9974999999999997E-2</v>
       </c>
       <c r="C23">
-        <v>1.3508587663552301E-2</v>
+        <v>9.7740436105545198E-3</v>
       </c>
       <c r="D23">
-        <v>2.78738863391172E-2</v>
+        <v>2.5649697341248098E-2</v>
       </c>
       <c r="E23">
-        <v>5.32056116716145E-2</v>
+        <v>5.0183058278950199E-2</v>
       </c>
       <c r="F23">
-        <v>6.8101215362548801</v>
+        <v>6.7317361831665004</v>
       </c>
       <c r="G23">
-        <v>2.3891453693172102</v>
+        <v>1.6367490443428501</v>
       </c>
       <c r="H23">
-        <v>4.7975658933116199</v>
+        <v>4.1079447867565504</v>
       </c>
       <c r="I23">
-        <v>9.0984522119104092</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>7.8441418673368002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.2016000000000002E-3</v>
+        <v>2.0347E-3</v>
       </c>
       <c r="C24">
-        <v>1.3844311700010399E-3</v>
+        <v>1.0908404126708899E-3</v>
       </c>
       <c r="D24">
-        <v>2.6945578541058401E-3</v>
+        <v>2.40408548333683E-3</v>
       </c>
       <c r="E24">
-        <v>3.9314179710316297E-3</v>
+        <v>3.9936359268895397E-3</v>
       </c>
       <c r="F24">
-        <v>16.985284805297901</v>
+        <v>14.1074895858765</v>
       </c>
       <c r="G24">
-        <v>9.2039841063614904</v>
+        <v>6.2567204342083098</v>
       </c>
       <c r="H24">
-        <v>17.020764679120798</v>
+        <v>14.9297900373203</v>
       </c>
       <c r="I24">
-        <v>27.183133371007099</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>26.470924526797699</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.15404999999999999</v>
+        <v>0.14742</v>
       </c>
       <c r="C25">
-        <v>9.2318839350601603E-2</v>
+        <v>8.3831661394552101E-2</v>
       </c>
       <c r="D25">
-        <v>0.12896191736798099</v>
+        <v>0.117287411538105</v>
       </c>
       <c r="E25">
-        <v>0.18461011176355699</v>
+        <v>0.16863696708333401</v>
       </c>
       <c r="F25">
-        <v>53.297542572021499</v>
+        <v>53.0390434265137</v>
       </c>
       <c r="G25">
-        <v>36.371442281125397</v>
+        <v>31.4171460641419</v>
       </c>
       <c r="H25">
-        <v>48.556447751886303</v>
+        <v>45.115575811814601</v>
       </c>
       <c r="I25">
-        <v>59.527135155113797</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>57.210974035725201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2844,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>6.4740156558592903E-4</v>
+        <v>7.90383263212314E-4</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -2856,36 +2882,36 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>3.2039311320077402</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3.16343805406057</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.10763</v>
+        <v>0.10508000000000001</v>
       </c>
       <c r="C27">
-        <v>7.5938077929497499E-2</v>
+        <v>6.8371952250723206E-2</v>
       </c>
       <c r="D27">
-        <v>9.6656762297283497E-2</v>
+        <v>8.9506657326629296E-2</v>
       </c>
       <c r="E27">
-        <v>0.131742802410796</v>
+        <v>0.119131162550652</v>
       </c>
       <c r="F27">
-        <v>87.734550476074205</v>
+        <v>87.859771728515597</v>
       </c>
       <c r="G27">
-        <v>71.194049649445205</v>
+        <v>65.439340922741707</v>
       </c>
       <c r="H27">
-        <v>80.772603873085501</v>
+        <v>80.357294846981304</v>
       </c>
       <c r="I27">
-        <v>88.789899659147295</v>
+        <v>88.518476672364898</v>
       </c>
     </row>
   </sheetData>
@@ -2894,11 +2920,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2354A6AE-8A13-4E78-A462-C21B225376E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{915C8AEA-BA7B-428E-86C9-2CBD4786A0B3}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2927,587 +2953,587 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.24334</v>
+        <v>0.50748000000000004</v>
       </c>
       <c r="C2">
-        <v>0.19558536108000901</v>
+        <v>0.37071565010266999</v>
       </c>
       <c r="D2">
-        <v>0.238226063795798</v>
+        <v>0.47248930509695503</v>
       </c>
       <c r="E2">
-        <v>0.27022960934048701</v>
+        <v>0.54965526537902998</v>
       </c>
       <c r="F2">
-        <v>23.803453445434599</v>
+        <v>47.626781463622997</v>
       </c>
       <c r="G2">
-        <v>18.960717046570299</v>
+        <v>37.839328719858599</v>
       </c>
       <c r="H2">
-        <v>23.264185975514</v>
+        <v>46.376341448226398</v>
       </c>
       <c r="I2">
-        <v>26.874922742361601</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53.101767174494299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.1155999999999997E-2</v>
+        <v>0.14940999999999999</v>
       </c>
       <c r="C3">
-        <v>4.4592143700647097E-2</v>
+        <v>0.11059614682270801</v>
       </c>
       <c r="D3">
-        <v>7.7439268322746294E-2</v>
+        <v>0.144703628565403</v>
       </c>
       <c r="E3">
-        <v>9.7743805861209093E-2</v>
+        <v>0.183749615105399</v>
       </c>
       <c r="F3">
-        <v>18.864336013793899</v>
+        <v>35.324127197265597</v>
       </c>
       <c r="G3">
-        <v>10.7213410888999</v>
+        <v>29.367157982230498</v>
       </c>
       <c r="H3">
-        <v>20.181406167016799</v>
+        <v>36.808571735189602</v>
       </c>
       <c r="I3">
-        <v>26.031311992475899</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>44.7226961211963</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.1903000000000003E-2</v>
+        <v>7.7374999999999999E-2</v>
       </c>
       <c r="C4">
-        <v>3.3286695357690202E-2</v>
+        <v>5.8546015425406703E-2</v>
       </c>
       <c r="D4">
-        <v>4.0170541396619498E-2</v>
+        <v>7.2848274786981096E-2</v>
       </c>
       <c r="E4">
-        <v>4.8451252131212597E-2</v>
+        <v>8.1513448178030704E-2</v>
       </c>
       <c r="F4">
-        <v>26.910623550415</v>
+        <v>48.023754119872997</v>
       </c>
       <c r="G4">
-        <v>21.158966646754902</v>
+        <v>40.611234741603703</v>
       </c>
       <c r="H4">
-        <v>25.742937988205401</v>
+        <v>47.323777418322202</v>
       </c>
       <c r="I4">
-        <v>31.519454809351299</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>52.094762654234799</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>7.2096999999999994E-2</v>
+        <v>9.7423999999999997E-2</v>
       </c>
       <c r="C5">
-        <v>5.8531897924029297E-2</v>
+        <v>6.7335367071421598E-2</v>
       </c>
       <c r="D5">
-        <v>6.8337108926691495E-2</v>
+        <v>9.1606409788129395E-2</v>
       </c>
       <c r="E5">
-        <v>7.9225216955969097E-2</v>
+        <v>0.109910788830221</v>
       </c>
       <c r="F5">
-        <v>32.268898010253899</v>
+        <v>42.265460968017599</v>
       </c>
       <c r="G5">
-        <v>25.874268254652598</v>
+        <v>32.2287318895456</v>
       </c>
       <c r="H5">
-        <v>30.654855232711501</v>
+        <v>41.222584887048697</v>
       </c>
       <c r="I5">
-        <v>35.815934987112698</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>47.817653016512203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.17208999999999999</v>
+        <v>0.28255000000000002</v>
       </c>
       <c r="C6">
-        <v>0.103809799789642</v>
+        <v>0.22088580490620499</v>
       </c>
       <c r="D6">
-        <v>0.16870802107489999</v>
+        <v>0.26729286337691399</v>
       </c>
       <c r="E6">
-        <v>0.213443186747208</v>
+        <v>0.33022490014524902</v>
       </c>
       <c r="F6">
-        <v>28.1267795562744</v>
+        <v>43.551502227783203</v>
       </c>
       <c r="G6">
-        <v>16.9670090180946</v>
+        <v>38.400880159315399</v>
       </c>
       <c r="H6">
-        <v>28.183055618485898</v>
+        <v>43.836620210597502</v>
       </c>
       <c r="I6">
-        <v>36.510928777551399</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>50.150823164446699</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.1111000000000001E-2</v>
+        <v>3.4978000000000001E-3</v>
       </c>
       <c r="C7">
-        <v>1.5318198908918499E-2</v>
+        <v>1.2720762794963E-3</v>
       </c>
       <c r="D7">
-        <v>1.90497884591165E-2</v>
+        <v>3.5552738946248502E-3</v>
       </c>
       <c r="E7">
-        <v>2.2847656950707899E-2</v>
+        <v>1.92505634813122E-2</v>
       </c>
       <c r="F7">
-        <v>56.118667602539098</v>
+        <v>8.2788763046264595</v>
       </c>
       <c r="G7">
-        <v>40.040146044685201</v>
+        <v>3.0379135248911902</v>
       </c>
       <c r="H7">
-        <v>51.369302329958899</v>
+        <v>9.1949513045186908</v>
       </c>
       <c r="I7">
-        <v>60.224235290522799</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46.916994348303497</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>3.4486000000000003E-2</v>
+        <v>3.3820999999999997E-2</v>
       </c>
       <c r="C8">
-        <v>2.7219658564695E-2</v>
+        <v>2.2193076057018101E-2</v>
       </c>
       <c r="D8">
-        <v>3.3077683799872297E-2</v>
+        <v>3.1828098749908898E-2</v>
       </c>
       <c r="E8">
-        <v>4.09486894122131E-2</v>
+        <v>4.05256733339922E-2</v>
       </c>
       <c r="F8">
-        <v>38.039535522460902</v>
+        <v>36.226005554199197</v>
       </c>
       <c r="G8">
-        <v>27.546608470183301</v>
+        <v>26.058525615099899</v>
       </c>
       <c r="H8">
-        <v>35.929346938961501</v>
+        <v>34.5799186639493</v>
       </c>
       <c r="I8">
-        <v>45.917600432596501</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>42.376289373574302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.3816E-2</v>
+        <v>1.6667999999999999E-2</v>
       </c>
       <c r="C9">
-        <v>1.07923050270224E-2</v>
+        <v>1.1402296766672201E-2</v>
       </c>
       <c r="D9">
-        <v>1.32214809557714E-2</v>
+        <v>1.5641320860357501E-2</v>
       </c>
       <c r="E9">
-        <v>1.5867661360562502E-2</v>
+        <v>2.0165454679764001E-2</v>
       </c>
       <c r="F9">
-        <v>32.733573913574197</v>
+        <v>38.194236755371101</v>
       </c>
       <c r="G9">
-        <v>22.519732577801499</v>
+        <v>29.037270742508099</v>
       </c>
       <c r="H9">
-        <v>30.832050378650798</v>
+        <v>36.550127110376899</v>
       </c>
       <c r="I9">
-        <v>38.946597251998703</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>43.286174479860001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>3.9481000000000002E-2</v>
+        <v>3.5090000000000003E-2</v>
       </c>
       <c r="C10">
-        <v>3.0792560534971598E-2</v>
+        <v>2.3263914964454499E-2</v>
       </c>
       <c r="D10">
-        <v>3.7180595280641902E-2</v>
+        <v>3.3857689725934503E-2</v>
       </c>
       <c r="E10">
-        <v>4.4774667827359699E-2</v>
+        <v>4.7922008262488699E-2</v>
       </c>
       <c r="F10">
-        <v>34.717826843261697</v>
+        <v>29.765403747558601</v>
       </c>
       <c r="G10">
-        <v>23.3514672909754</v>
+        <v>21.174921511954299</v>
       </c>
       <c r="H10">
-        <v>32.005379500022499</v>
+        <v>28.9818645927955</v>
       </c>
       <c r="I10">
-        <v>40.7270498281326</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>37.214706355887103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>6.7648999999999999E-3</v>
+        <v>0.17102000000000001</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.117620243622118</v>
       </c>
       <c r="D11">
-        <v>7.8747037463451196E-3</v>
+        <v>0.15782839274499399</v>
       </c>
       <c r="E11">
-        <v>4.3550845581923403E-2</v>
+        <v>0.184275852397351</v>
       </c>
       <c r="F11">
-        <v>2.8883967399597199</v>
+        <v>56.321361541747997</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>44.334391256579401</v>
       </c>
       <c r="H11">
-        <v>2.8413788912186502</v>
+        <v>54.094275774526103</v>
       </c>
       <c r="I11">
-        <v>16.374218933554701</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>69.713446241172207</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.26556999999999997</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.23398655415233499</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.24904719319523699</v>
       </c>
       <c r="E12">
-        <v>2.3027109257182699E-2</v>
+        <v>0.26577694680772801</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>58.677684783935497</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>53.902916302076498</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>57.975783991008797</v>
       </c>
       <c r="I12">
-        <v>5.4091208747287096</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>65.337247138925093</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>3.9350000000000003E-2</v>
+        <v>1.7194999999999998E-2</v>
       </c>
       <c r="C13">
-        <v>3.06580446733167E-2</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>3.8038503778347298E-2</v>
+        <v>1.5698293318868201E-2</v>
       </c>
       <c r="E13">
-        <v>4.6561914039726197E-2</v>
+        <v>2.60144194581916E-2</v>
       </c>
       <c r="F13">
-        <v>51.265903472900398</v>
+        <v>23.128456115722699</v>
       </c>
       <c r="G13">
-        <v>40.398175822943003</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>49.495330581042801</v>
+        <v>21.2957472541285</v>
       </c>
       <c r="I13">
-        <v>57.642942949981197</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>34.749188626104697</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>5.1041000000000003E-2</v>
+        <v>1.0626E-2</v>
       </c>
       <c r="C14">
-        <v>3.64707222859251E-2</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>4.9567097467648098E-2</v>
+        <v>1.12031875983246E-2</v>
       </c>
       <c r="E14">
-        <v>6.4997586103803795E-2</v>
+        <v>2.68053591874945E-2</v>
       </c>
       <c r="F14">
-        <v>49.288612365722699</v>
+        <v>12.610050201416</v>
       </c>
       <c r="G14">
-        <v>38.304730402205898</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>48.026629434759997</v>
+        <v>11.0335801480201</v>
       </c>
       <c r="I14">
-        <v>57.416628602376299</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>27.738419575879401</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>3.9348000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>2.5320417407726999E-2</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>3.8803200606108798E-2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>5.3013723712462602E-2</v>
+        <v>5.5680006665368396E-3</v>
       </c>
       <c r="F15">
-        <v>33.578037261962898</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>19.446386599202601</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>30.879372421642401</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>48.138057585489001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>4.3712679949518103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.0924999999999999E-2</v>
+        <v>2.5305000000000001E-2</v>
       </c>
       <c r="C16">
-        <v>1.5971724640465701E-2</v>
+        <v>1.8644362047706999E-2</v>
       </c>
       <c r="D16">
-        <v>2.1362428233197402E-2</v>
+        <v>2.5093217538648901E-2</v>
       </c>
       <c r="E16">
-        <v>2.7315663966249199E-2</v>
+        <v>3.1909478763689499E-2</v>
       </c>
       <c r="F16">
-        <v>20.580093383789102</v>
+        <v>21.6320705413818</v>
       </c>
       <c r="G16">
-        <v>14.272515642875501</v>
+        <v>15.367846677897299</v>
       </c>
       <c r="H16">
-        <v>19.322230465815299</v>
+        <v>22.004208183378601</v>
       </c>
       <c r="I16">
-        <v>26.072076198626899</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>27.782668277591299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1.5478E-2</v>
+        <v>0.12751000000000001</v>
       </c>
       <c r="C17">
-        <v>1.0164127938467099E-2</v>
+        <v>0.112260190816835</v>
       </c>
       <c r="D17">
-        <v>1.78424374002908E-2</v>
+        <v>0.120103343717989</v>
       </c>
       <c r="E17">
-        <v>2.53319835920966E-2</v>
+        <v>0.12839826407848501</v>
       </c>
       <c r="F17">
-        <v>6.9355483055114702</v>
+        <v>45.734855651855497</v>
       </c>
       <c r="G17">
-        <v>3.8567504398284802</v>
+        <v>42.169424301006501</v>
       </c>
       <c r="H17">
-        <v>6.9109667007231899</v>
+        <v>45.417662315687103</v>
       </c>
       <c r="I17">
-        <v>10.0195601190891</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>49.795280208457001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>3.6198000000000001E-2</v>
+        <v>7.6581999999999997E-2</v>
       </c>
       <c r="C18">
-        <v>2.3969491553619399E-2</v>
+        <v>6.0370263367526003E-2</v>
       </c>
       <c r="D18">
-        <v>3.4754353434183698E-2</v>
+        <v>7.4308252775338507E-2</v>
       </c>
       <c r="E18">
-        <v>5.3473751022083398E-2</v>
+        <v>9.3549612639742402E-2</v>
       </c>
       <c r="F18">
-        <v>17.912168502807599</v>
+        <v>32.999385833740199</v>
       </c>
       <c r="G18">
-        <v>9.9341125642527395</v>
+        <v>28.704103473096598</v>
       </c>
       <c r="H18">
-        <v>15.8297205888506</v>
+        <v>33.366302429351897</v>
       </c>
       <c r="I18">
-        <v>26.0322726196434</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>38.255763876615703</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4.4697000000000001E-2</v>
+        <v>0.25463000000000002</v>
       </c>
       <c r="C19">
-        <v>3.3273519572749898E-2</v>
+        <v>0.22217823051569199</v>
       </c>
       <c r="D19">
-        <v>4.9367078341187802E-2</v>
+        <v>0.242097697396807</v>
       </c>
       <c r="E19">
-        <v>6.6843358732784006E-2</v>
+        <v>0.2624880529177</v>
       </c>
       <c r="F19">
-        <v>8.9131917953491193</v>
+        <v>40.5486030578613</v>
       </c>
       <c r="G19">
-        <v>5.6796029895525901</v>
+        <v>37.303213100831897</v>
       </c>
       <c r="H19">
-        <v>8.5342813241585809</v>
+        <v>40.628056635824201</v>
       </c>
       <c r="I19">
-        <v>12.2655838927923</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>44.446001894262103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>0.31607000000000002</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.26692926361685798</v>
       </c>
       <c r="D20">
-        <v>8.7031055279216101E-3</v>
+        <v>0.30314360933419199</v>
       </c>
       <c r="E20">
-        <v>4.5484995079607099E-2</v>
+        <v>0.35680963886273798</v>
       </c>
       <c r="F20">
-        <v>1.0834165811538701</v>
+        <v>36.388057708740199</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>32.898435337664601</v>
       </c>
       <c r="H20">
-        <v>1.1490722583764801</v>
+        <v>37.188936315661103</v>
       </c>
       <c r="I20">
-        <v>5.7409987905777902</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>42.205768920790398</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>8.5006999999999999E-2</v>
+        <v>0.89959999999999996</v>
       </c>
       <c r="C21">
-        <v>7.3086876932867806E-2</v>
+        <v>0.73646656969532498</v>
       </c>
       <c r="D21">
-        <v>0.126017882957081</v>
+        <v>0.84311310230272496</v>
       </c>
       <c r="E21">
-        <v>0.193434901074373</v>
+        <v>0.92485151779546904</v>
       </c>
       <c r="F21">
-        <v>5.6108245849609402</v>
+        <v>39.1140747070313</v>
       </c>
       <c r="G21">
-        <v>3.63860715986696</v>
+        <v>35.110197563988599</v>
       </c>
       <c r="H21">
-        <v>6.3741031648338202</v>
+        <v>38.9642317536997</v>
       </c>
       <c r="I21">
-        <v>9.9980545655068909</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>42.046943875295099</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -3521,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>1.32796818612683E-2</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -3533,152 +3559,152 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>12.968419450899599</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.10001</v>
+        <v>0.10372000000000001</v>
       </c>
       <c r="C23">
-        <v>5.9909844029956402E-2</v>
+        <v>6.8101127371213405E-2</v>
       </c>
       <c r="D23">
-        <v>9.8819105520070893E-2</v>
+        <v>0.108044119568633</v>
       </c>
       <c r="E23">
-        <v>0.15270646410340399</v>
+        <v>0.15555750744109401</v>
       </c>
       <c r="F23">
-        <v>19.191501617431602</v>
+        <v>16.434352874755898</v>
       </c>
       <c r="G23">
-        <v>10.055159201168999</v>
+        <v>10.788560244723501</v>
       </c>
       <c r="H23">
-        <v>16.970837847673401</v>
+        <v>17.437336388122802</v>
       </c>
       <c r="I23">
-        <v>28.8855782532085</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>24.913869611733102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1.0854E-4</v>
+        <v>8.1948000000000003E-3</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>5.3204235405127998E-3</v>
       </c>
       <c r="D24">
-        <v>9.0286498163697098E-5</v>
+        <v>7.8905519766549904E-3</v>
       </c>
       <c r="E24">
-        <v>1.17553538730381E-3</v>
+        <v>1.2174257680339201E-2</v>
       </c>
       <c r="F24">
-        <v>0.97718054056167603</v>
+        <v>47.159008026122997</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>34.626837193113097</v>
       </c>
       <c r="H24">
-        <v>0.54192043348111896</v>
+        <v>49.404595694967199</v>
       </c>
       <c r="I24">
-        <v>7.8283611706775904</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>67.900610519371895</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.11791</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>8.2968382166302396E-2</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0.119994544615633</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>0.149260488571343</v>
+        <v>9.4487029163835504E-3</v>
       </c>
       <c r="F25">
-        <v>43.750370025634801</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>27.820591931642401</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>44.978604314486098</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>56.643520256748403</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3.44202910550506</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>4.9798999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>4.6130831430722701E-4</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>4.5919262807739697E-3</v>
+        <v>1.8501383313566299E-3</v>
       </c>
       <c r="E26">
-        <v>7.3844842715491098E-3</v>
+        <v>5.80496146535763E-3</v>
       </c>
       <c r="F26">
-        <v>26.533565521240199</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>1.5376882699890499</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>23.303550641851601</v>
+        <v>7.8438076512546298</v>
       </c>
       <c r="I26">
-        <v>46.252595881211803</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>21.301508312669501</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>1.2070000000000001E-2</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>7.5654660061481704E-3</v>
       </c>
       <c r="D27">
-        <v>7.3914356649264204E-3</v>
+        <v>9.79048109238502E-3</v>
       </c>
       <c r="E27">
-        <v>2.1247540742297202E-2</v>
+        <v>2.2266616740758201E-2</v>
       </c>
       <c r="F27">
-        <v>2.8825521469116202</v>
+        <v>8.7818155288696307</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>6.1701100920344496</v>
       </c>
       <c r="H27">
-        <v>6.4166666295537897</v>
+        <v>8.9345402750889207</v>
       </c>
       <c r="I27">
-        <v>18.3724551099493</v>
+        <v>16.554758045799801</v>
       </c>
     </row>
   </sheetData>
@@ -3687,11 +3713,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9954EF2-970B-4C00-B23F-2E542FE2F7AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1231F6B2-80CF-4D9D-8028-35E57C26BC28}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3720,758 +3746,839 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.13053999999999999</v>
+        <v>0.10165</v>
       </c>
       <c r="C2">
-        <v>7.5648086409997595E-2</v>
+        <v>7.1044134759279898E-2</v>
       </c>
       <c r="D2">
-        <v>0.13045879560270099</v>
+        <v>0.107343462604629</v>
       </c>
       <c r="E2">
-        <v>0.18300066104261001</v>
+        <v>0.14630911241662001</v>
       </c>
       <c r="F2">
-        <v>13.1651659011841</v>
+        <v>11.9854431152344</v>
       </c>
       <c r="G2">
-        <v>7.6646013203642296</v>
+        <v>6.9162266215622603</v>
       </c>
       <c r="H2">
-        <v>12.618059895188599</v>
+        <v>10.462169655659199</v>
       </c>
       <c r="I2">
-        <v>17.9838300107462</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>14.5767387884211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.0500000000000001E-2</v>
+        <v>6.1929999999999999E-2</v>
       </c>
       <c r="C3">
-        <v>4.0355691121493802E-3</v>
+        <v>3.92407942345252E-2</v>
       </c>
       <c r="D3">
-        <v>1.4295815856629901E-2</v>
+        <v>6.8187491517629997E-2</v>
       </c>
       <c r="E3">
-        <v>2.6802979338462998E-2</v>
+        <v>0.10200996879027301</v>
       </c>
       <c r="F3">
-        <v>3.2831444740295401</v>
+        <v>17.633205413818398</v>
       </c>
       <c r="G3">
-        <v>1.03787229151946</v>
+        <v>9.9302415751791298</v>
       </c>
       <c r="H3">
-        <v>3.7090814863130301</v>
+        <v>17.5518058572078</v>
       </c>
       <c r="I3">
-        <v>6.8404299212117703</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>24.886194356638001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.6206000000000002E-2</v>
+        <v>1.1726E-2</v>
       </c>
       <c r="C4">
-        <v>9.2627181930049502E-3</v>
+        <v>6.5636366112469102E-3</v>
       </c>
       <c r="D4">
-        <v>1.6124073794391298E-2</v>
+        <v>1.2148677338955E-2</v>
       </c>
       <c r="E4">
-        <v>2.3630033924766699E-2</v>
+        <v>1.8210167714821701E-2</v>
       </c>
       <c r="F4">
-        <v>10.8320398330688</v>
+        <v>9.6360912322997994</v>
       </c>
       <c r="G4">
-        <v>6.0359319687032604</v>
+        <v>4.2327881150877502</v>
       </c>
       <c r="H4">
-        <v>10.3552193342964</v>
+        <v>7.8243608277804597</v>
       </c>
       <c r="I4">
-        <v>15.2141953058466</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11.9094645934418</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3.0709E-2</v>
+        <v>1.3818E-2</v>
       </c>
       <c r="C5">
-        <v>1.3868594104689999E-2</v>
+        <v>8.4532213016146E-3</v>
       </c>
       <c r="D5">
-        <v>2.97539028310588E-2</v>
+        <v>1.5856564434446899E-2</v>
       </c>
       <c r="E5">
-        <v>4.7045275633730801E-2</v>
+        <v>2.62186268116778E-2</v>
       </c>
       <c r="F5">
-        <v>13.8824872970581</v>
+        <v>7.7367024421691903</v>
       </c>
       <c r="G5">
-        <v>6.42015586013774</v>
+        <v>3.7328859401135501</v>
       </c>
       <c r="H5">
-        <v>13.1150867942149</v>
+        <v>7.1381124053918903</v>
       </c>
       <c r="I5">
-        <v>21.193861141975599</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12.4004886727319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>9.7361000000000003E-2</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>5.9051431579440899E-2</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.106052868814211</v>
       </c>
       <c r="E6">
-        <v>4.6404552899274596E-3</v>
+        <v>0.15177438650591901</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>18.644126892089801</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>10.2711257896991</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>17.511947738499501</v>
       </c>
       <c r="I6">
-        <v>0.79291099043663704</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>23.398055760344199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7.7457999999999997E-3</v>
+        <v>2.0078000000000001E-3</v>
       </c>
       <c r="C7">
-        <v>4.7231059421276502E-3</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>7.09539302252958E-3</v>
+        <v>3.3822508190830798E-3</v>
       </c>
       <c r="E7">
-        <v>9.7883061948044903E-3</v>
+        <v>8.8757559242368493E-3</v>
       </c>
       <c r="F7">
-        <v>20.118553161621101</v>
+        <v>4.120361328125</v>
       </c>
       <c r="G7">
-        <v>11.474988557233999</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>19.1056174800676</v>
+        <v>8.6043853718301193</v>
       </c>
       <c r="I7">
-        <v>25.897397626548599</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>22.261958040988201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.1795999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>9.5241712608327006E-3</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2.04610523228432E-2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>2.9823762862697101E-2</v>
+        <v>3.7566604443184299E-3</v>
       </c>
       <c r="F8">
-        <v>23.0953159332275</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>10.7895535062195</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>21.7657150141454</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>32.618696459044898</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>4.0956792407315703</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.1660999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>6.5510950900573598E-3</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1.1016726090850601E-2</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1.4348110813737099E-2</v>
+        <v>1.6143035717348501E-3</v>
       </c>
       <c r="F9">
-        <v>26.616458892822301</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>14.8522527472562</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>24.943722349222298</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>34.060866749495098</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3.7646959118740799</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>4.0391999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>2.3955371315682102E-2</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>3.8236650720392902E-2</v>
+        <v>1.94215709928829E-3</v>
       </c>
       <c r="E10">
-        <v>5.05022814139576E-2</v>
+        <v>7.8088262575073996E-3</v>
       </c>
       <c r="F10">
-        <v>33.809028625488303</v>
+        <v>2.1229403093457201E-2</v>
       </c>
       <c r="G10">
-        <v>19.742988018989202</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>32.143788705590303</v>
+        <v>1.63298007089582</v>
       </c>
       <c r="I10">
-        <v>43.365754246530898</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>7.1818767736476303</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>6.5951999999999997E-2</v>
+        <v>3.4265999999999998E-2</v>
       </c>
       <c r="C11">
-        <v>4.1957461992891201E-2</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>6.5569409917659097E-2</v>
+        <v>2.4870937389486501E-2</v>
       </c>
       <c r="E11">
-        <v>8.4749045536814893E-2</v>
+        <v>6.2927738003000097E-2</v>
       </c>
       <c r="F11">
-        <v>23.64133644104</v>
+        <v>15.4918880462646</v>
       </c>
       <c r="G11">
-        <v>15.4765931786007</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>23.1683128824425</v>
+        <v>8.7084744172668902</v>
       </c>
       <c r="I11">
-        <v>29.764013472954101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>21.022391949361602</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>7.7607999999999996E-2</v>
+        <v>5.1976000000000001E-2</v>
       </c>
       <c r="C12">
-        <v>6.6849417141712997E-2</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>7.9862282417664701E-2</v>
+        <v>5.4045501262660001E-2</v>
       </c>
       <c r="E12">
-        <v>9.5894977181488497E-2</v>
+        <v>7.9293154297516294E-2</v>
       </c>
       <c r="F12">
-        <v>19.168724060058601</v>
+        <v>15.7830047607422</v>
       </c>
       <c r="G12">
-        <v>15.961152394312199</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>18.840782836989</v>
+        <v>12.2918632755686</v>
       </c>
       <c r="I12">
-        <v>22.353718498248199</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17.887990368388301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.0712E-3</v>
+        <v>6.8998999999999996E-3</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>3.2521164720502601E-4</v>
       </c>
       <c r="D13">
-        <v>1.53172154948363E-3</v>
+        <v>9.9472399882603695E-3</v>
       </c>
       <c r="E13">
-        <v>3.9269050566394098E-2</v>
+        <v>2.7899488114099799E-2</v>
       </c>
       <c r="F13">
-        <v>2.0931930541992201</v>
+        <v>9.1248521804809606</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.43089244213294697</v>
       </c>
       <c r="H13">
-        <v>2.1276178608986198</v>
+        <v>12.7043160204326</v>
       </c>
       <c r="I13">
-        <v>41.984146198476701</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>30.441738563043799</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>3.5978999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>2.03919994717973E-2</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>3.0105886412280802E-2</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>5.6163252006114002E-2</v>
+        <v>2.4789667406152301E-2</v>
       </c>
       <c r="F14">
-        <v>30.5425930023193</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>18.576068763336099</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>29.5441159515042</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>48.991012909326003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>21.321606386556901</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>7.9693E-2</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>5.0721028388571003E-2</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>7.8051085664110897E-2</v>
+        <v>5.7402433331566203E-3</v>
       </c>
       <c r="E15">
-        <v>9.4020912244134502E-2</v>
+        <v>2.71193151082962E-2</v>
       </c>
       <c r="F15">
-        <v>61.088909149169901</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>49.438510914410401</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>62.341585241779903</v>
+        <v>4.5302252312473303</v>
       </c>
       <c r="I15">
-        <v>71.562681817829798</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>21.156904822783499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>5.1956000000000002E-2</v>
+        <v>7.9944000000000005E-3</v>
       </c>
       <c r="C16">
-        <v>4.1402623383019303E-2</v>
+        <v>6.37433556288891E-3</v>
       </c>
       <c r="D16">
-        <v>5.0280787965594799E-2</v>
+        <v>1.14424971608317E-2</v>
       </c>
       <c r="E16">
-        <v>5.9004603908008997E-2</v>
+        <v>2.0560329906828999E-2</v>
       </c>
       <c r="F16">
-        <v>45.447891235351598</v>
+        <v>7.3490552902221697</v>
       </c>
       <c r="G16">
-        <v>39.173505371144202</v>
+        <v>5.6007707942632399</v>
       </c>
       <c r="H16">
-        <v>45.410618607300897</v>
+        <v>9.9138222733508208</v>
       </c>
       <c r="I16">
-        <v>51.945466351887703</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17.291497384778399</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>8.0782999999999994E-2</v>
+        <v>2.6178E-2</v>
       </c>
       <c r="C17">
-        <v>6.7804878674830496E-2</v>
+        <v>1.0176744645117201E-2</v>
       </c>
       <c r="D17">
-        <v>8.0190777901840399E-2</v>
+        <v>2.9204152231922E-2</v>
       </c>
       <c r="E17">
-        <v>8.7124768132975094E-2</v>
+        <v>4.1117760942179497E-2</v>
       </c>
       <c r="F17">
-        <v>31.419958114623999</v>
+        <v>12.1954555511475</v>
       </c>
       <c r="G17">
-        <v>26.883312905129799</v>
+        <v>4.0135857420357901</v>
       </c>
       <c r="H17">
-        <v>30.9827569579498</v>
+        <v>10.853050027895099</v>
       </c>
       <c r="I17">
-        <v>33.478287482819198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15.112109854881099</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.10796</v>
+        <v>1.0522000000000001E-3</v>
       </c>
       <c r="C18">
-        <v>7.5736444028227906E-2</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0.103569485727771</v>
+        <v>5.1685432141342202E-3</v>
       </c>
       <c r="E18">
-        <v>0.122324975438075</v>
+        <v>1.6893290419269898E-2</v>
       </c>
       <c r="F18">
-        <v>48.2115287780762</v>
+        <v>2.0368185043335001</v>
       </c>
       <c r="G18">
-        <v>35.839797205877197</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>46.828864610650903</v>
+        <v>2.26615246104158</v>
       </c>
       <c r="I18">
-        <v>54.351792405295697</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>7.3263918905028396</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.20548</v>
+        <v>5.2308E-2</v>
       </c>
       <c r="C19">
-        <v>0.17548877964045601</v>
+        <v>2.80122820405991E-2</v>
       </c>
       <c r="D19">
-        <v>0.20224016717295101</v>
+        <v>6.0790472036665197E-2</v>
       </c>
       <c r="E19">
-        <v>0.21944464045276599</v>
+        <v>8.8625850786269597E-2</v>
       </c>
       <c r="F19">
-        <v>35.3833198547363</v>
+        <v>10.730725288391101</v>
       </c>
       <c r="G19">
-        <v>31.306111801492701</v>
+        <v>4.9421963505381603</v>
       </c>
       <c r="H19">
-        <v>35.076373323882102</v>
+        <v>10.154008054457</v>
       </c>
       <c r="I19">
-        <v>37.3762606302056</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>14.302178069382499</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.29022999999999999</v>
+        <v>5.8058999999999999E-2</v>
       </c>
       <c r="C20">
-        <v>0.25861824933487898</v>
+        <v>9.5884737373934104E-3</v>
       </c>
       <c r="D20">
-        <v>0.28802249455988499</v>
+        <v>7.8409461733050898E-2</v>
       </c>
       <c r="E20">
-        <v>0.33978694881569099</v>
+        <v>0.11173115900733201</v>
       </c>
       <c r="F20">
-        <v>36.992427825927699</v>
+        <v>9.3899879455566406</v>
       </c>
       <c r="G20">
-        <v>32.437699886560097</v>
+        <v>1.1879486866048701</v>
       </c>
       <c r="H20">
-        <v>37.379421626032702</v>
+        <v>9.4590530417312095</v>
       </c>
       <c r="I20">
-        <v>43.287959763359702</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13.260071616405201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.57172000000000001</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="C21">
-        <v>0.473857073151083</v>
+        <v>0.18374057688821399</v>
       </c>
       <c r="D21">
-        <v>0.57791797508970899</v>
+        <v>0.30199858147192099</v>
       </c>
       <c r="E21">
-        <v>0.69536240000149496</v>
+        <v>0.37394684479738999</v>
       </c>
       <c r="F21">
-        <v>28.547527313232401</v>
+        <v>14.2855882644653</v>
       </c>
       <c r="G21">
-        <v>23.9046854937734</v>
+        <v>8.5259419445820193</v>
       </c>
       <c r="H21">
-        <v>29.246656401128199</v>
+        <v>13.860657924803901</v>
       </c>
       <c r="I21">
-        <v>35.654087416227199</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17.186702373337098</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>3.1140000000000001E-2</v>
+        <v>6.1520999999999999E-2</v>
       </c>
       <c r="C22">
-        <v>1.8531706988885999E-2</v>
+        <v>2.4722530833182901E-2</v>
       </c>
       <c r="D22">
-        <v>3.0253427445413698E-2</v>
+        <v>7.0958574761318394E-2</v>
       </c>
       <c r="E22">
-        <v>5.6509574455306702E-2</v>
+        <v>0.112077585365415</v>
       </c>
       <c r="F22">
-        <v>28.403814315795898</v>
+        <v>41.714073181152301</v>
       </c>
       <c r="G22">
-        <v>16.866246421035601</v>
+        <v>17.537124011998198</v>
       </c>
       <c r="H22">
-        <v>28.532708765444202</v>
+        <v>48.685173933578902</v>
       </c>
       <c r="I22">
-        <v>48.450349340370799</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>61.447508774933098</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.37411</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0.29697825734288502</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0.357808503429835</v>
+        <v>1.7090297724082101E-2</v>
       </c>
       <c r="E23">
-        <v>0.39050616549623501</v>
+        <v>5.7802483830983499E-2</v>
       </c>
       <c r="F23">
-        <v>61.372406005859403</v>
+        <v>0.23314584791660301</v>
       </c>
       <c r="G23">
-        <v>54.7115755333378</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>61.443376940897103</v>
+        <v>2.8045723729813199</v>
       </c>
       <c r="I23">
-        <v>66.984344562702304</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>8.8038147252714207</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>8.6176999999999998E-4</v>
+        <v>3.9436000000000002E-3</v>
       </c>
       <c r="C24">
-        <v>5.9127610387059296E-4</v>
+        <v>8.8393110736128904E-4</v>
       </c>
       <c r="D24">
-        <v>1.1319052055248501E-3</v>
+        <v>3.8761826041844899E-3</v>
       </c>
       <c r="E24">
-        <v>2.2844491232140102E-3</v>
+        <v>6.3132168480059302E-3</v>
       </c>
       <c r="F24">
-        <v>6.8816170692443803</v>
+        <v>29.070959091186499</v>
       </c>
       <c r="G24">
-        <v>3.4899873256523102</v>
+        <v>5.9382028855719797</v>
       </c>
       <c r="H24">
-        <v>7.5883758475922596</v>
+        <v>24.072623951375199</v>
       </c>
       <c r="I24">
-        <v>14.339015500634099</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>35.973068853061598</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>5.2494999999999998E-3</v>
+        <v>9.6016000000000001E-3</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>3.6966593522916001E-3</v>
+        <v>1.4293206044627801E-2</v>
       </c>
       <c r="E25">
-        <v>4.9875500163813202E-3</v>
+        <v>0.111602660799846</v>
       </c>
       <c r="F25">
-        <v>1.5009298324585001</v>
+        <v>3.2378766536712602</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>1.335898251538</v>
+        <v>5.9168631133691196</v>
       </c>
       <c r="I25">
-        <v>2.0256995917815201</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>33.405348058872001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>6.1073999999999998E-7</v>
+        <v>1.6289000000000001E-2</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1.0721637561306801E-2</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1.75334116822707E-2</v>
       </c>
       <c r="E26">
-        <v>6.7978146563626497E-4</v>
+        <v>3.3069807777574303E-2</v>
       </c>
       <c r="F26">
-        <v>0.94049417972564697</v>
+        <v>78.321578979492202</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>62.270379543397098</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>78.481567686846603</v>
       </c>
       <c r="I26">
-        <v>4.3965634753829299</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>90.290550905992006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>2.0856E-3</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>1.7115312213174701E-3</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>1.2310256109422201E-2</v>
+        <v>2.39983328626013E-2</v>
       </c>
       <c r="F27">
-        <v>1.4832090139389</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>1.4144251760140101</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>9.2949926036989901</v>
+        <v>18.8997493190003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7C53CE0-3DFA-034D-87C8-D94BA23282D4}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.1640625" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/results/interim_results/pmf_results/allsites_pmf_bs_fpeak.xlsx
+++ b/results/interim_results/pmf_results/allsites_pmf_bs_fpeak.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lf649/git_repos/active/thriveair_analysis/results/interim_results/pmf_results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drexel0-my.sharepoint.com/personal/lf649_drexel_edu/Documents/Desktop/pmf_02_03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381C32B6-68FD-FD4E-9138-E6AC149E32A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{B5A24587-7615-4B94-8414-B13DE9C2204D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D285307-3925-479E-BBEA-CC488B40D9C6}"/>
   <bookViews>
-    <workbookView xWindow="14860" yWindow="6580" windowWidth="21800" windowHeight="11220" activeTab="5" xr2:uid="{BE83C13A-3955-4331-9143-64E0083985C4}"/>
+    <workbookView xWindow="7515" yWindow="3045" windowWidth="21795" windowHeight="11220" activeTab="4" xr2:uid="{A9E7DD8E-DE23-4676-B34C-5578062BF486}"/>
   </bookViews>
   <sheets>
     <sheet name="Factor 1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Factor 3" sheetId="3" r:id="rId3"/>
     <sheet name="Factor 4" sheetId="4" r:id="rId4"/>
     <sheet name="Factor 5" sheetId="5" r:id="rId5"/>
-    <sheet name="Key" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="35">
   <si>
     <t>Species</t>
   </si>
@@ -124,16 +123,16 @@
     <t>trichloromonofluoromethane</t>
   </si>
   <si>
-    <t>Fpeak Value_conc</t>
+    <t>Fpeak Value conc</t>
   </si>
   <si>
-    <t>BS 5th_conc</t>
+    <t>BS 5th conc</t>
   </si>
   <si>
-    <t>BS Median_conc</t>
+    <t>BS Median conc</t>
   </si>
   <si>
-    <t>BS 95th_conc</t>
+    <t>BS 95th conc</t>
   </si>
   <si>
     <t>Fpeak Value pct</t>
@@ -146,30 +145,6 @@
   </si>
   <si>
     <t>BS 95th pct</t>
-  </si>
-  <si>
-    <t>Factor Number</t>
-  </si>
-  <si>
-    <t>Percent Mass explained</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Gasoline evaporation</t>
-  </si>
-  <si>
-    <t>Petroleum solvents</t>
-  </si>
-  <si>
-    <t>Background/Legacy</t>
-  </si>
-  <si>
-    <t>Vehicle exhaust</t>
-  </si>
-  <si>
-    <t>Auto repair industry</t>
   </si>
 </sst>
 </file>
@@ -205,9 +180,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,11 +515,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F381CA0D-A984-4B31-BD67-67D4D79C1842}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E635BFE3-9755-40A1-B15D-C8881D35B618}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -574,297 +548,297 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.23433000000000001</v>
+        <v>0.23055999999999999</v>
       </c>
       <c r="C2">
-        <v>0.20333576291146899</v>
+        <v>0.20168590596640301</v>
       </c>
       <c r="D2">
-        <v>0.23650971326516201</v>
+        <v>0.23289048573396501</v>
       </c>
       <c r="E2">
-        <v>0.26729856543900599</v>
+        <v>0.26399284572938497</v>
       </c>
       <c r="F2">
-        <v>23.3832302093506</v>
+        <v>23.348741531372099</v>
       </c>
       <c r="G2">
-        <v>19.665276039453801</v>
+        <v>20.021887197411999</v>
       </c>
       <c r="H2">
-        <v>23.266280319629701</v>
+        <v>23.313666456044601</v>
       </c>
       <c r="I2">
-        <v>26.706593381755699</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>26.922069233404201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.1820999999999996E-2</v>
+        <v>7.0897000000000002E-2</v>
       </c>
       <c r="C3">
-        <v>5.14418339916465E-2</v>
+        <v>4.8644898141583702E-2</v>
       </c>
       <c r="D3">
-        <v>7.6089067248938796E-2</v>
+        <v>7.3841558396387105E-2</v>
       </c>
       <c r="E3">
-        <v>9.7246725299768202E-2</v>
+        <v>9.4287737335197699E-2</v>
       </c>
       <c r="F3">
-        <v>19.1255283355713</v>
+        <v>19.1073322296143</v>
       </c>
       <c r="G3">
-        <v>12.208550671805501</v>
+        <v>11.969197922737999</v>
       </c>
       <c r="H3">
-        <v>19.475242929230301</v>
+        <v>19.443401783968</v>
       </c>
       <c r="I3">
-        <v>24.9188048990681</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>25.2141400530762</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.2008999999999998E-2</v>
+        <v>4.1345E-2</v>
       </c>
       <c r="C4">
-        <v>3.5742177755241203E-2</v>
+        <v>3.53195273501134E-2</v>
       </c>
       <c r="D4">
-        <v>4.1543346781135998E-2</v>
+        <v>4.1329776924467203E-2</v>
       </c>
       <c r="E4">
-        <v>4.8778110229772298E-2</v>
+        <v>4.91349288455852E-2</v>
       </c>
       <c r="F4">
-        <v>27.572746276855501</v>
+        <v>27.542413711547901</v>
       </c>
       <c r="G4">
-        <v>23.103145919498701</v>
+        <v>23.3094639602844</v>
       </c>
       <c r="H4">
-        <v>27.163937425294701</v>
+        <v>27.282116032330102</v>
       </c>
       <c r="I4">
-        <v>32.069287244517199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>32.1721769212377</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>7.2021000000000002E-2</v>
+        <v>7.0862999999999995E-2</v>
       </c>
       <c r="C5">
-        <v>6.1227130076573898E-2</v>
+        <v>5.9465610035932003E-2</v>
       </c>
       <c r="D5">
-        <v>6.9352140941810997E-2</v>
+        <v>6.9121168273031899E-2</v>
       </c>
       <c r="E5">
-        <v>7.9789485527358206E-2</v>
+        <v>7.9457723340763106E-2</v>
       </c>
       <c r="F5">
-        <v>32.731925964355497</v>
+        <v>32.687534332275398</v>
       </c>
       <c r="G5">
-        <v>27.460226538189399</v>
+        <v>27.661153953462399</v>
       </c>
       <c r="H5">
-        <v>31.641434330748702</v>
+        <v>31.906168399872499</v>
       </c>
       <c r="I5">
-        <v>35.727308679751999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>36.005453360053501</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.16683000000000001</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="C6">
-        <v>0.107747108303553</v>
+        <v>9.8981385065741695E-2</v>
       </c>
       <c r="D6">
-        <v>0.16501369497752499</v>
+        <v>0.162673872587941</v>
       </c>
       <c r="E6">
-        <v>0.205648955168415</v>
+        <v>0.20258247505917701</v>
       </c>
       <c r="F6">
-        <v>28.001768112182599</v>
+        <v>27.9700031280518</v>
       </c>
       <c r="G6">
-        <v>16.271478470030601</v>
+        <v>15.621990192584001</v>
       </c>
       <c r="H6">
-        <v>27.566282682777899</v>
+        <v>27.635284770384899</v>
       </c>
       <c r="I6">
-        <v>35.893128041847298</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>35.355063882969702</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.1256000000000001E-2</v>
+        <v>2.0936E-2</v>
       </c>
       <c r="C7">
-        <v>1.24042775031866E-2</v>
+        <v>1.2012920428434701E-2</v>
       </c>
       <c r="D7">
-        <v>1.9142234930979201E-2</v>
+        <v>1.88289960883272E-2</v>
       </c>
       <c r="E7">
-        <v>2.6511395884647002E-2</v>
+        <v>2.6127855665504698E-2</v>
       </c>
       <c r="F7">
-        <v>55.430652618408203</v>
+        <v>55.366008758544901</v>
       </c>
       <c r="G7">
-        <v>30.496920512152801</v>
+        <v>30.86334629601</v>
       </c>
       <c r="H7">
-        <v>49.378587010639599</v>
+        <v>49.631066110617802</v>
       </c>
       <c r="I7">
-        <v>58.987221325710898</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>59.019437963214799</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>3.5757999999999998E-2</v>
+        <v>3.517E-2</v>
       </c>
       <c r="C8">
-        <v>2.73242244312847E-2</v>
+        <v>2.65805515417522E-2</v>
       </c>
       <c r="D8">
-        <v>3.5020475189575302E-2</v>
+        <v>3.4774077395172902E-2</v>
       </c>
       <c r="E8">
-        <v>4.50718440484578E-2</v>
+        <v>4.3752080031418103E-2</v>
       </c>
       <c r="F8">
-        <v>39.084800720214801</v>
+        <v>39.028694152832003</v>
       </c>
       <c r="G8">
-        <v>30.1175061227678</v>
+        <v>29.9157597214076</v>
       </c>
       <c r="H8">
-        <v>38.101802529896801</v>
+        <v>38.5048302052327</v>
       </c>
       <c r="I8">
-        <v>47.3622596304307</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>47.207098223888202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.4308E-2</v>
+        <v>1.4076E-2</v>
       </c>
       <c r="C9">
-        <v>1.12359463506059E-2</v>
+        <v>1.1080610876459399E-2</v>
       </c>
       <c r="D9">
-        <v>1.40462191617948E-2</v>
+        <v>1.3820206593811901E-2</v>
       </c>
       <c r="E9">
-        <v>1.7555745587779201E-2</v>
+        <v>1.69413561905318E-2</v>
       </c>
       <c r="F9">
-        <v>33.646373748779297</v>
+        <v>33.602798461914098</v>
       </c>
       <c r="G9">
-        <v>25.7546206233969</v>
+        <v>26.195481894149399</v>
       </c>
       <c r="H9">
-        <v>32.552094012584902</v>
+        <v>32.702851770641601</v>
       </c>
       <c r="I9">
-        <v>40.858824465191603</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>40.870244553178203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>4.0836999999999998E-2</v>
+        <v>4.0148000000000003E-2</v>
       </c>
       <c r="C10">
-        <v>2.91621797375082E-2</v>
+        <v>2.89137614612184E-2</v>
       </c>
       <c r="D10">
-        <v>3.8851697216037699E-2</v>
+        <v>3.8196635363157698E-2</v>
       </c>
       <c r="E10">
-        <v>4.9829809885687998E-2</v>
+        <v>4.9291714093533702E-2</v>
       </c>
       <c r="F10">
-        <v>34.886669158935497</v>
+        <v>34.819126129150398</v>
       </c>
       <c r="G10">
-        <v>24.408244971397899</v>
+        <v>24.924061443922501</v>
       </c>
       <c r="H10">
-        <v>32.889460783243301</v>
+        <v>32.896076020366699</v>
       </c>
       <c r="I10">
-        <v>42.068106255548997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>42.838103336848498</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4.8224000000000001E-3</v>
+        <v>4.5728000000000001E-3</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1.0853433400494101E-2</v>
+        <v>1.0823244792983199E-2</v>
       </c>
       <c r="E11">
-        <v>4.7566344986095202E-2</v>
+        <v>4.5197360101626498E-2</v>
       </c>
       <c r="F11">
-        <v>1.80223441123962</v>
+        <v>1.7472231388092001</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>4.0651668469694098</v>
+        <v>4.2038905493962497</v>
       </c>
       <c r="I11">
-        <v>18.063023966803701</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17.726797918482902</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -878,7 +852,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>2.6790134692621599E-2</v>
+        <v>2.5830758816298899E-2</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -890,213 +864,213 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>6.1461505947079997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.8289065013169399</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>3.9461999999999997E-2</v>
+        <v>3.8837999999999998E-2</v>
       </c>
       <c r="C13">
-        <v>2.82401135941301E-2</v>
+        <v>2.4801218152891699E-2</v>
       </c>
       <c r="D13">
-        <v>3.76850805280129E-2</v>
+        <v>3.7045456652061201E-2</v>
       </c>
       <c r="E13">
-        <v>4.80575476439365E-2</v>
+        <v>4.8287585000660702E-2</v>
       </c>
       <c r="F13">
-        <v>52.121994018554702</v>
+        <v>52.047695159912102</v>
       </c>
       <c r="G13">
-        <v>36.591625308674402</v>
+        <v>34.049026250711101</v>
       </c>
       <c r="H13">
-        <v>48.088153054772199</v>
+        <v>48.673595990007797</v>
       </c>
       <c r="I13">
-        <v>57.978759000894698</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>58.622735871210999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>5.4406999999999997E-2</v>
+        <v>5.3529E-2</v>
       </c>
       <c r="C14">
-        <v>3.3202199670747501E-2</v>
+        <v>3.23478181080653E-2</v>
       </c>
       <c r="D14">
-        <v>5.0973795259511699E-2</v>
+        <v>4.96981358916724E-2</v>
       </c>
       <c r="E14">
-        <v>7.2470667520223894E-2</v>
+        <v>6.9896313344489397E-2</v>
       </c>
       <c r="F14">
-        <v>52.308391571044901</v>
+        <v>52.221500396728501</v>
       </c>
       <c r="G14">
-        <v>34.521514464457901</v>
+        <v>34.149220821205503</v>
       </c>
       <c r="H14">
-        <v>48.851911814603</v>
+        <v>48.9868265657271</v>
       </c>
       <c r="I14">
-        <v>60.855884756151603</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>60.2813541800395</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>4.3123000000000002E-2</v>
+        <v>4.2369999999999998E-2</v>
       </c>
       <c r="C15">
-        <v>2.0104593892970399E-2</v>
+        <v>2.1571473556470201E-2</v>
       </c>
       <c r="D15">
-        <v>3.99252134826601E-2</v>
+        <v>3.84314848123938E-2</v>
       </c>
       <c r="E15">
-        <v>5.4825271486491099E-2</v>
+        <v>5.33091855976245E-2</v>
       </c>
       <c r="F15">
-        <v>33.564174652099602</v>
+        <v>33.443771362304702</v>
       </c>
       <c r="G15">
-        <v>16.1191098272209</v>
+        <v>17.395169743533199</v>
       </c>
       <c r="H15">
-        <v>30.701711250860502</v>
+        <v>30.365044421278899</v>
       </c>
       <c r="I15">
-        <v>43.459580743332701</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>42.813269173028601</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.0976999999999999E-2</v>
+        <v>2.0608000000000001E-2</v>
       </c>
       <c r="C16">
-        <v>1.3857590490339E-2</v>
+        <v>1.3237494280364699E-2</v>
       </c>
       <c r="D16">
-        <v>1.9854812351002699E-2</v>
+        <v>1.9608269922011101E-2</v>
       </c>
       <c r="E16">
-        <v>2.63576649498065E-2</v>
+        <v>2.62072708932698E-2</v>
       </c>
       <c r="F16">
-        <v>18.791954040527301</v>
+        <v>18.712486267089801</v>
       </c>
       <c r="G16">
-        <v>11.838584268264</v>
+        <v>11.731196153687099</v>
       </c>
       <c r="H16">
-        <v>17.278788211247399</v>
+        <v>17.408686405781999</v>
       </c>
       <c r="I16">
-        <v>23.838473965231199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23.452969587528401</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1.6188000000000001E-2</v>
+        <v>1.5869000000000001E-2</v>
       </c>
       <c r="C17">
-        <v>1.1441554933391201E-2</v>
+        <v>1.1769023752558E-2</v>
       </c>
       <c r="D17">
-        <v>1.8123249062833299E-2</v>
+        <v>1.83525145970788E-2</v>
       </c>
       <c r="E17">
-        <v>2.5680449180722799E-2</v>
+        <v>2.4501686531443301E-2</v>
       </c>
       <c r="F17">
-        <v>6.5469498634338397</v>
+        <v>6.5152897834777797</v>
       </c>
       <c r="G17">
-        <v>4.2672479443101903</v>
+        <v>4.42082740497119</v>
       </c>
       <c r="H17">
-        <v>6.8540001001247299</v>
+        <v>7.0195388348158696</v>
       </c>
       <c r="I17">
-        <v>10.0801482592922</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9.6107920826019697</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>3.8519999999999999E-2</v>
+        <v>3.7804999999999998E-2</v>
       </c>
       <c r="C18">
-        <v>2.3120592084282899E-2</v>
+        <v>2.3757759572516201E-2</v>
       </c>
       <c r="D18">
-        <v>3.6913463509545601E-2</v>
+        <v>3.6001668826461698E-2</v>
       </c>
       <c r="E18">
-        <v>5.5385526825291E-2</v>
+        <v>5.45038645970531E-2</v>
       </c>
       <c r="F18">
-        <v>17.246515274047901</v>
+        <v>17.185661315918001</v>
       </c>
       <c r="G18">
-        <v>9.8313898875188706</v>
+        <v>10.193329924759</v>
       </c>
       <c r="H18">
-        <v>16.254247060007401</v>
+        <v>16.1778169429464</v>
       </c>
       <c r="I18">
-        <v>26.1377990643442</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>26.941129161402198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4.6163999999999997E-2</v>
+        <v>4.5272E-2</v>
       </c>
       <c r="C19">
-        <v>3.3102668237756101E-2</v>
+        <v>3.2987416495877303E-2</v>
       </c>
       <c r="D19">
-        <v>4.8966010879751401E-2</v>
+        <v>4.8537268683970597E-2</v>
       </c>
       <c r="E19">
-        <v>6.3832722486098101E-2</v>
+        <v>6.1392231033254703E-2</v>
       </c>
       <c r="F19">
-        <v>8.1537513732910192</v>
+        <v>8.1123638153076207</v>
       </c>
       <c r="G19">
-        <v>5.5533490176714997</v>
+        <v>5.5425657543114699</v>
       </c>
       <c r="H19">
-        <v>8.2610011676753192</v>
+        <v>8.2663505675901394</v>
       </c>
       <c r="I19">
-        <v>11.2159190617544</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+        <v>11.115377041108699</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1110,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>2.34665684387752E-2</v>
+        <v>2.2750880959663499E-2</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1122,39 +1096,39 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>2.7618044122942602</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2.74538108855455</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>4.4329E-2</v>
+        <v>4.3394000000000002E-2</v>
       </c>
       <c r="C21">
-        <v>2.3658132043617702E-2</v>
+        <v>2.23511139408634E-2</v>
       </c>
       <c r="D21">
-        <v>6.7302376476896103E-2</v>
+        <v>6.5094925369163004E-2</v>
       </c>
       <c r="E21">
-        <v>0.125939655624528</v>
+        <v>0.118763229392261</v>
       </c>
       <c r="F21">
-        <v>2.5235321521759002</v>
+        <v>2.4891426563262899</v>
       </c>
       <c r="G21">
-        <v>1.09344237299528</v>
+        <v>1.0767796982209401</v>
       </c>
       <c r="H21">
-        <v>3.11202421122201</v>
+        <v>3.06967580340774</v>
       </c>
       <c r="I21">
-        <v>5.76206795855372</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.5326651194587901</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1168,10 +1142,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>1.8611732237580701E-2</v>
+        <v>1.7217040072416898E-2</v>
       </c>
       <c r="F22">
-        <v>0.22666272521019001</v>
+        <v>7.7477671205997495E-2</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1180,152 +1154,152 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>13.3847279075635</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>13.236782750672599</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.10389</v>
+        <v>0.10196</v>
       </c>
       <c r="C23">
-        <v>4.2489857480738198E-2</v>
+        <v>4.2709490248314601E-2</v>
       </c>
       <c r="D23">
-        <v>9.2739614840767398E-2</v>
+        <v>9.0380663270018494E-2</v>
       </c>
       <c r="E23">
-        <v>0.153354975716439</v>
+        <v>0.15550527249361901</v>
       </c>
       <c r="F23">
-        <v>16.8649597167969</v>
+        <v>16.7802219390869</v>
       </c>
       <c r="G23">
-        <v>6.7305660972841199</v>
+        <v>7.1915962226009098</v>
       </c>
       <c r="H23">
-        <v>14.9436934754916</v>
+        <v>14.7892223521263</v>
       </c>
       <c r="I23">
-        <v>25.386791167089999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <v>26.702847710572499</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>3.9442999999999998E-4</v>
+        <v>3.9723999999999998E-4</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>4.7777593925154698E-4</v>
+        <v>4.20158231888198E-4</v>
       </c>
       <c r="E24">
-        <v>2.3432908685788499E-3</v>
+        <v>2.4907006301536599E-3</v>
       </c>
       <c r="F24">
-        <v>2.87548160552979</v>
+        <v>2.8652396202087398</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>2.8655539893470299</v>
+        <v>2.6421989250023001</v>
       </c>
       <c r="I24">
-        <v>14.5180283416985</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+        <v>16.459160146337101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.11899999999999999</v>
+        <v>0.11735</v>
       </c>
       <c r="C25">
-        <v>8.1467131259040398E-2</v>
+        <v>8.0688474386532594E-2</v>
       </c>
       <c r="D25">
-        <v>0.113482151248066</v>
+        <v>0.110205246792509</v>
       </c>
       <c r="E25">
-        <v>0.14639225172451101</v>
+        <v>0.135516294325599</v>
       </c>
       <c r="F25">
-        <v>43.398204803466797</v>
+        <v>43.402370452880902</v>
       </c>
       <c r="G25">
-        <v>26.130722261464499</v>
+        <v>25.128230534328502</v>
       </c>
       <c r="H25">
-        <v>43.665244291226998</v>
+        <v>43.103940338398701</v>
       </c>
       <c r="I25">
-        <v>57.500386323853597</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+        <v>55.150214818366202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>3.4762999999999999E-3</v>
+        <v>3.4058999999999999E-3</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>2.4087060887728498E-3</v>
+        <v>2.31683180729656E-3</v>
       </c>
       <c r="E26">
-        <v>6.1967319622095798E-3</v>
+        <v>6.1162855163303604E-3</v>
       </c>
       <c r="F26">
-        <v>19.8954887390137</v>
+        <v>19.673906326293899</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>10.767446530042999</v>
+        <v>10.5103358880369</v>
       </c>
       <c r="I26">
-        <v>33.624644257084903</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+        <v>35.776235904329297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>2.8614999999999999E-3</v>
+        <v>2.9605E-3</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>7.0573997534280003E-3</v>
+        <v>6.2600125141249003E-3</v>
       </c>
       <c r="E27">
-        <v>2.22011563486538E-2</v>
+        <v>1.9442851599245699E-2</v>
       </c>
       <c r="F27">
-        <v>3.3584139347076398</v>
+        <v>3.3745105266571001</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>6.3821365213568297</v>
+        <v>5.9051046392807001</v>
       </c>
       <c r="I27">
-        <v>20.022304758028401</v>
+        <v>17.259280760365101</v>
       </c>
     </row>
   </sheetData>
@@ -1334,11 +1308,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{461724D2-7A8D-4294-B04B-FE123235B1E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1E20E28-DE87-4549-B302-6EA7AA3F9561}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1367,758 +1341,758 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.14985999999999999</v>
+        <v>0.49782999999999999</v>
       </c>
       <c r="C2">
-        <v>0.10016345266011201</v>
+        <v>0.36562773962565198</v>
       </c>
       <c r="D2">
-        <v>0.154134868290875</v>
+        <v>0.46093988165490002</v>
       </c>
       <c r="E2">
-        <v>0.21124434612463799</v>
+        <v>0.54799537573447699</v>
       </c>
       <c r="F2">
-        <v>14.813480377197299</v>
+        <v>47.499473571777301</v>
       </c>
       <c r="G2">
-        <v>10.067914887212099</v>
+        <v>37.315240956846601</v>
       </c>
       <c r="H2">
-        <v>14.9209318948326</v>
+        <v>45.9350553995979</v>
       </c>
       <c r="I2">
-        <v>20.935862711278901</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>53.198233813392001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.1495E-2</v>
+        <v>0.1464</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.10573129124257299</v>
       </c>
       <c r="D3">
-        <v>1.31588818800931E-2</v>
+        <v>0.14073866377555599</v>
       </c>
       <c r="E3">
-        <v>2.5603702331973201E-2</v>
+        <v>0.183768013670768</v>
       </c>
       <c r="F3">
-        <v>3.43089771270752</v>
+        <v>35.248367309570298</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>29.555484358876502</v>
       </c>
       <c r="H3">
-        <v>3.3964055012077501</v>
+        <v>36.404023557463901</v>
       </c>
       <c r="I3">
-        <v>6.3492813135272703</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>45.064849153486001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.8634999999999999E-2</v>
+        <v>7.5898999999999994E-2</v>
       </c>
       <c r="C4">
-        <v>1.4575341527967699E-2</v>
+        <v>5.7408980174613003E-2</v>
       </c>
       <c r="D4">
-        <v>1.9217903145679699E-2</v>
+        <v>7.0785165486589099E-2</v>
       </c>
       <c r="E4">
-        <v>2.5004728431401502E-2</v>
+        <v>8.1362330722478504E-2</v>
       </c>
       <c r="F4">
-        <v>12.249279975891101</v>
+        <v>47.8987846374512</v>
       </c>
       <c r="G4">
-        <v>9.3968101713147494</v>
+        <v>39.8414565967554</v>
       </c>
       <c r="H4">
-        <v>12.440306963997299</v>
+        <v>46.834326532148999</v>
       </c>
       <c r="I4">
-        <v>16.712822204867901</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>52.076724902854103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3.4728000000000002E-2</v>
+        <v>9.5588000000000006E-2</v>
       </c>
       <c r="C5">
-        <v>2.14419417356762E-2</v>
+        <v>6.5107816815242095E-2</v>
       </c>
       <c r="D5">
-        <v>3.4626763076063001E-2</v>
+        <v>8.8978223368627499E-2</v>
       </c>
       <c r="E5">
-        <v>5.1887748768880602E-2</v>
+        <v>0.10770983489642801</v>
       </c>
       <c r="F5">
-        <v>15.6225776672363</v>
+        <v>42.162273406982401</v>
       </c>
       <c r="G5">
-        <v>9.8079264480923207</v>
+        <v>31.5719693503776</v>
       </c>
       <c r="H5">
-        <v>15.6197601387773</v>
+        <v>40.858091343601998</v>
       </c>
       <c r="I5">
-        <v>24.0319515767548</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>48.041779621834102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.27723999999999999</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.21477238587941999</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.262707905543829</v>
       </c>
       <c r="E6">
-        <v>2.3321317476647199E-2</v>
+        <v>0.32102308288435799</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>43.4380073547363</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>38.077642051505698</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>43.8177724410914</v>
       </c>
       <c r="I6">
-        <v>3.4897067199381899</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>50.174184248000699</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8.1436000000000008E-3</v>
+        <v>3.4269999999999999E-3</v>
       </c>
       <c r="C7">
-        <v>2.9879052766780601E-3</v>
+        <v>1.2656653083792601E-3</v>
       </c>
       <c r="D7">
-        <v>7.5382121042336797E-3</v>
+        <v>3.5991450081945199E-3</v>
       </c>
       <c r="E7">
-        <v>1.4220572532387701E-2</v>
+        <v>1.8146089874470799E-2</v>
       </c>
       <c r="F7">
-        <v>21.2289123535156</v>
+        <v>8.3194971084594709</v>
       </c>
       <c r="G7">
-        <v>7.2416093696884296</v>
+        <v>2.9479360578090699</v>
       </c>
       <c r="H7">
-        <v>19.013277833429701</v>
+        <v>9.6206805110262206</v>
       </c>
       <c r="I7">
-        <v>32.440461121817101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>46.163847499037701</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.3441E-2</v>
+        <v>3.3204999999999998E-2</v>
       </c>
       <c r="C8">
-        <v>1.4645706781991201E-2</v>
+        <v>2.06628298220424E-2</v>
       </c>
       <c r="D8">
-        <v>2.2423335524703401E-2</v>
+        <v>3.1581738906137302E-2</v>
       </c>
       <c r="E8">
-        <v>2.9912148266448099E-2</v>
+        <v>4.0455243613421801E-2</v>
       </c>
       <c r="F8">
-        <v>24.689191818237301</v>
+        <v>36.149250030517599</v>
       </c>
       <c r="G8">
-        <v>16.143170890142201</v>
+        <v>24.903693968113199</v>
       </c>
       <c r="H8">
-        <v>24.2600783095704</v>
+        <v>34.733349265351698</v>
       </c>
       <c r="I8">
-        <v>33.649660837823497</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>42.602065259629697</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.2367E-2</v>
+        <v>1.6362999999999999E-2</v>
       </c>
       <c r="C9">
-        <v>9.1991169078180692E-3</v>
+        <v>1.12420883297346E-2</v>
       </c>
       <c r="D9">
-        <v>1.2002739685412401E-2</v>
+        <v>1.54189326579107E-2</v>
       </c>
       <c r="E9">
-        <v>1.44175434975273E-2</v>
+        <v>1.9783304409936898E-2</v>
       </c>
       <c r="F9">
-        <v>27.975894927978501</v>
+        <v>38.1062202453613</v>
       </c>
       <c r="G9">
-        <v>21.505061319834901</v>
+        <v>28.737367872531301</v>
       </c>
       <c r="H9">
-        <v>27.785138934365801</v>
+        <v>36.592323686882203</v>
       </c>
       <c r="I9">
-        <v>34.875309958621301</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>43.5369260813601</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>4.233E-2</v>
+        <v>3.4424999999999997E-2</v>
       </c>
       <c r="C10">
-        <v>3.08700011451409E-2</v>
+        <v>2.1852177867927199E-2</v>
       </c>
       <c r="D10">
-        <v>4.1079059346395601E-2</v>
+        <v>3.3041346488386601E-2</v>
       </c>
       <c r="E10">
-        <v>5.0229439631711698E-2</v>
+        <v>4.6721683947330103E-2</v>
       </c>
       <c r="F10">
-        <v>35.024604797363303</v>
+        <v>29.6956691741943</v>
       </c>
       <c r="G10">
-        <v>26.344010082760501</v>
+        <v>20.320113625803302</v>
       </c>
       <c r="H10">
-        <v>34.394985444823902</v>
+        <v>28.607515614407401</v>
       </c>
       <c r="I10">
-        <v>43.3112630390251</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>37.117580220502099</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>6.9775000000000004E-2</v>
+        <v>0.16757</v>
       </c>
       <c r="C11">
-        <v>3.76247627143909E-2</v>
+        <v>0.11487213280315101</v>
       </c>
       <c r="D11">
-        <v>6.9115178576722405E-2</v>
+        <v>0.151045227762</v>
       </c>
       <c r="E11">
-        <v>7.7734095528100899E-2</v>
+        <v>0.18053291040160899</v>
       </c>
       <c r="F11">
-        <v>24.665889739990199</v>
+        <v>56.061477661132798</v>
       </c>
       <c r="G11">
-        <v>14.350560993858901</v>
+        <v>43.503735882393997</v>
       </c>
       <c r="H11">
-        <v>24.393908561071999</v>
+        <v>52.213019939991398</v>
       </c>
       <c r="I11">
-        <v>27.730538290822299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>68.230686584971494</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>8.4320000000000006E-2</v>
+        <v>0.26046999999999998</v>
       </c>
       <c r="C12">
-        <v>6.9487733893760395E-2</v>
+        <v>0.229752326738277</v>
       </c>
       <c r="D12">
-        <v>8.45630323249493E-2</v>
+        <v>0.244252427417637</v>
       </c>
       <c r="E12">
-        <v>0.10111935835767399</v>
+        <v>0.25929416230178798</v>
       </c>
       <c r="F12">
-        <v>20.110898971557599</v>
+        <v>58.513782501220703</v>
       </c>
       <c r="G12">
-        <v>15.718500746116</v>
+        <v>53.392353096071503</v>
       </c>
       <c r="H12">
-        <v>19.730138313711802</v>
+        <v>57.952870995411701</v>
       </c>
       <c r="I12">
-        <v>24.877377736140499</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>64.870630801554796</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.2440000000000001E-3</v>
+        <v>1.6889999999999999E-2</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>3.7789517474440699E-4</v>
       </c>
       <c r="D13">
-        <v>1.04050217185007E-3</v>
+        <v>1.53155832506952E-2</v>
       </c>
       <c r="E13">
-        <v>3.1590296752418499E-2</v>
+        <v>2.5407296384794002E-2</v>
       </c>
       <c r="F13">
-        <v>1.4498751163482699</v>
+        <v>23.101354598998999</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.41138884281764898</v>
       </c>
       <c r="H13">
-        <v>1.3998909266810899</v>
+        <v>20.944306854800001</v>
       </c>
       <c r="I13">
-        <v>32.5216523892555</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>34.462986660524699</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.6450000000000001E-2</v>
+        <v>1.042E-2</v>
       </c>
       <c r="C14">
-        <v>1.56762762256684E-2</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>2.41423993766746E-2</v>
+        <v>1.16186523242192E-2</v>
       </c>
       <c r="E14">
-        <v>5.3274493327095197E-2</v>
+        <v>2.5001771492194701E-2</v>
       </c>
       <c r="F14">
-        <v>23.128421783447301</v>
+        <v>12.5999917984009</v>
       </c>
       <c r="G14">
-        <v>15.7442953148439</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>24.453295906754501</v>
+        <v>11.8246318051303</v>
       </c>
       <c r="I14">
-        <v>43.923087526341398</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>25.5289551373506</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>7.8543000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>5.1664011788926899E-2</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>7.8252667132656203E-2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>9.8233791109409996E-2</v>
+        <v>6.0346258530663199E-3</v>
       </c>
       <c r="F15">
-        <v>59.481922149658203</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>42.9456861850406</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>60.5641152383443</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>71.965889650559205</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.92287399864541</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>5.2142000000000001E-2</v>
+        <v>2.4830000000000001E-2</v>
       </c>
       <c r="C16">
-        <v>4.32530584812717E-2</v>
+        <v>1.8440282097068699E-2</v>
       </c>
       <c r="D16">
-        <v>5.0872008838790499E-2</v>
+        <v>2.4511643394527001E-2</v>
       </c>
       <c r="E16">
-        <v>6.17218178508799E-2</v>
+        <v>3.0739149919320901E-2</v>
       </c>
       <c r="F16">
-        <v>44.765583038330099</v>
+        <v>21.5766792297363</v>
       </c>
       <c r="G16">
-        <v>38.951718936690099</v>
+        <v>15.8214046492444</v>
       </c>
       <c r="H16">
-        <v>44.542123201644202</v>
+        <v>21.887092121271799</v>
       </c>
       <c r="I16">
-        <v>50.782738253135598</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>27.3571376750936</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>8.3049999999999999E-2</v>
+        <v>0.12512000000000001</v>
       </c>
       <c r="C17">
-        <v>6.9841038279331996E-2</v>
+        <v>0.108872504139821</v>
       </c>
       <c r="D17">
-        <v>8.2768314801538095E-2</v>
+        <v>0.116726954156259</v>
       </c>
       <c r="E17">
-        <v>8.8992032127020504E-2</v>
+        <v>0.12647224933175299</v>
       </c>
       <c r="F17">
-        <v>31.4079685211182</v>
+        <v>45.610118865966797</v>
       </c>
       <c r="G17">
-        <v>27.806988299459199</v>
+        <v>41.5130112330638</v>
       </c>
       <c r="H17">
-        <v>31.169138949463999</v>
+        <v>45.1446474207374</v>
       </c>
       <c r="I17">
-        <v>33.528629462151898</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+        <v>49.7629512513154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.10982</v>
+        <v>7.5152999999999998E-2</v>
       </c>
       <c r="C18">
-        <v>8.3978519901184795E-2</v>
+        <v>5.8986632444126698E-2</v>
       </c>
       <c r="D18">
-        <v>0.10719003872383299</v>
+        <v>7.16923685006014E-2</v>
       </c>
       <c r="E18">
-        <v>0.121405021729208</v>
+        <v>9.1883893987385404E-2</v>
       </c>
       <c r="F18">
-        <v>47.717281341552699</v>
+        <v>32.906566619872997</v>
       </c>
       <c r="G18">
-        <v>40.958445927678497</v>
+        <v>28.378308867331899</v>
       </c>
       <c r="H18">
-        <v>47.099107678542701</v>
+        <v>32.804774661146404</v>
       </c>
       <c r="I18">
-        <v>51.5893668675334</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>38.468942809525402</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.21101</v>
+        <v>0.24984000000000001</v>
       </c>
       <c r="C19">
-        <v>0.18179704301188701</v>
+        <v>0.21505669775873301</v>
       </c>
       <c r="D19">
-        <v>0.20928987989234299</v>
+        <v>0.23490014117299601</v>
       </c>
       <c r="E19">
-        <v>0.223628742980755</v>
+        <v>0.25798863273963901</v>
       </c>
       <c r="F19">
-        <v>35.238025665283203</v>
+        <v>40.437858581542997</v>
       </c>
       <c r="G19">
-        <v>31.8633098223481</v>
+        <v>36.581025225810599</v>
       </c>
       <c r="H19">
-        <v>35.010397612783301</v>
+        <v>40.271397438907698</v>
       </c>
       <c r="I19">
-        <v>37.026350970609798</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+        <v>44.023757339311402</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.30753999999999998</v>
+        <v>0.31013000000000002</v>
       </c>
       <c r="C20">
-        <v>0.28031245534157501</v>
+        <v>0.26198793925155101</v>
       </c>
       <c r="D20">
-        <v>0.30485772465946698</v>
+        <v>0.29937392506786697</v>
       </c>
       <c r="E20">
-        <v>0.33846907530952097</v>
+        <v>0.34745912118066202</v>
       </c>
       <c r="F20">
-        <v>37.332191467285199</v>
+        <v>36.291301727294901</v>
       </c>
       <c r="G20">
-        <v>33.242521659161198</v>
+        <v>33.083364946528498</v>
       </c>
       <c r="H20">
-        <v>37.345581899636102</v>
+        <v>37.241515609685301</v>
       </c>
       <c r="I20">
-        <v>41.971237422140902</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>42.209953034298699</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.66418999999999995</v>
+        <v>0.88266999999999995</v>
       </c>
       <c r="C21">
-        <v>0.59606255923903695</v>
+        <v>0.72751002048928004</v>
       </c>
       <c r="D21">
-        <v>0.665133725375603</v>
+        <v>0.83256454149753301</v>
       </c>
       <c r="E21">
-        <v>0.75115808618192503</v>
+        <v>0.90936865802586198</v>
       </c>
       <c r="F21">
-        <v>30.7431240081787</v>
+        <v>39.013877868652301</v>
       </c>
       <c r="G21">
-        <v>27.340302767300599</v>
+        <v>35.248806975129099</v>
       </c>
       <c r="H21">
-        <v>30.790036328409599</v>
+        <v>39.108313687284202</v>
       </c>
       <c r="I21">
-        <v>35.136710163694303</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+        <v>42.000143324762703</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>3.4640999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>2.30712852633169E-2</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>3.3540310192077899E-2</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>5.8666877016104603E-2</v>
+        <v>2.02396239479408E-3</v>
       </c>
       <c r="F22">
-        <v>23.9769992828369</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>16.3838497811123</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>22.944844937182001</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>34.866628462103399</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.39291056218413</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.38179000000000002</v>
+        <v>0.10174999999999999</v>
       </c>
       <c r="C23">
-        <v>0.29410120842194398</v>
+        <v>6.3399111547287001E-2</v>
       </c>
       <c r="D23">
-        <v>0.37109112779144898</v>
+        <v>0.104074642954412</v>
       </c>
       <c r="E23">
-        <v>0.40189613519602102</v>
+        <v>0.151228515236948</v>
       </c>
       <c r="F23">
-        <v>59.735805511474602</v>
+        <v>16.369256973266602</v>
       </c>
       <c r="G23">
-        <v>52.722059362361698</v>
+        <v>10.4312895917367</v>
       </c>
       <c r="H23">
-        <v>59.213674338428497</v>
+        <v>17.509197710288198</v>
       </c>
       <c r="I23">
-        <v>63.202793583536597</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <v>25.298932318258</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>9.1301999999999996E-4</v>
+        <v>8.0424999999999993E-3</v>
       </c>
       <c r="C24">
-        <v>2.04886555116665E-4</v>
+        <v>5.0507593510641302E-3</v>
       </c>
       <c r="D24">
-        <v>1.0365729964961199E-3</v>
+        <v>8.0019744483878202E-3</v>
       </c>
       <c r="E24">
-        <v>2.1715561260599999E-3</v>
+        <v>1.20076761473971E-2</v>
       </c>
       <c r="F24">
-        <v>6.7870597839355504</v>
+        <v>47.160324096679702</v>
       </c>
       <c r="G24">
-        <v>1.1520754790787799</v>
+        <v>33.850701635677297</v>
       </c>
       <c r="H24">
-        <v>6.4946760058391098</v>
+        <v>50.0215740150446</v>
       </c>
       <c r="I24">
-        <v>12.9911062947654</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+        <v>68.271790897219901</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>8.5428000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>7.4809189303632804E-4</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>3.1996224192465698E-3</v>
+        <v>1.3525604640639E-2</v>
       </c>
       <c r="F25">
-        <v>0.32487452030181901</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0.28589754886648699</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>1.2696350479068099</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.6324298903804104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>2.3541E-4</v>
+        <v>0</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1.7612737817841301E-3</v>
       </c>
       <c r="E26">
-        <v>4.6929459388900301E-4</v>
+        <v>5.37055993508153E-3</v>
       </c>
       <c r="F26">
-        <v>1.7829298973083501</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>7.4975242707233001</v>
       </c>
       <c r="I26">
-        <v>2.5802995570884</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+        <v>20.8432061362758</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>1.1776E-2</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>7.9157740730598902E-3</v>
       </c>
       <c r="D27">
-        <v>3.1736010671915298E-4</v>
+        <v>9.65753485325015E-3</v>
       </c>
       <c r="E27">
-        <v>3.1402083782528902E-3</v>
+        <v>2.1885098441164201E-2</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>8.7416877746581996</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>6.6510536161793299</v>
       </c>
       <c r="H27">
-        <v>0.24058496774667601</v>
+        <v>8.8623665781524892</v>
       </c>
       <c r="I27">
-        <v>2.3799094976417399</v>
+        <v>18.751092419217802</v>
       </c>
     </row>
   </sheetData>
@@ -2127,11 +2101,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1FEC3B-7305-4647-BABE-4DD44CA22496}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{798701D9-396F-4A15-ACE3-640BBBFBE300}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2160,181 +2134,181 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.7788000000000002E-2</v>
+        <v>1.8231000000000001E-2</v>
       </c>
       <c r="C2">
-        <v>1.4826727138037499E-2</v>
+        <v>1.2309425993398701E-2</v>
       </c>
       <c r="D2">
-        <v>5.4469681040830498E-2</v>
+        <v>5.0844887475636501E-2</v>
       </c>
       <c r="E2">
-        <v>8.2218739746002106E-2</v>
+        <v>8.2876496526978996E-2</v>
       </c>
       <c r="F2">
-        <v>2.1910643577575701</v>
+        <v>2.26468777656555</v>
       </c>
       <c r="G2">
-        <v>1.46987322127794</v>
+        <v>1.20994507627797</v>
       </c>
       <c r="H2">
-        <v>5.3305393781408501</v>
+        <v>5.0588901968364501</v>
       </c>
       <c r="I2">
-        <v>8.1221584357577896</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8.0538943556003293</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9.3227000000000004E-2</v>
+        <v>9.1686000000000004E-2</v>
       </c>
       <c r="C3">
-        <v>7.7422402149428304E-2</v>
+        <v>7.59911736297951E-2</v>
       </c>
       <c r="D3">
-        <v>8.9677141392463897E-2</v>
+        <v>8.8901377476985205E-2</v>
       </c>
       <c r="E3">
-        <v>0.106946293184458</v>
+        <v>0.107926869875104</v>
       </c>
       <c r="F3">
-        <v>24.486242294311499</v>
+        <v>24.498165130615199</v>
       </c>
       <c r="G3">
-        <v>19.901628597170401</v>
+        <v>20.0557587296083</v>
       </c>
       <c r="H3">
-        <v>22.958860688379598</v>
+        <v>23.176837293341102</v>
       </c>
       <c r="I3">
-        <v>26.8779644895953</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>27.7200812983912</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.2680000000000001E-3</v>
+        <v>3.3322999999999998E-3</v>
       </c>
       <c r="C4">
-        <v>2.1450416884850401E-3</v>
+        <v>2.1487892775030001E-3</v>
       </c>
       <c r="D4">
-        <v>8.6776596759335807E-3</v>
+        <v>8.1169227642674292E-3</v>
       </c>
       <c r="E4">
-        <v>1.31519830034306E-2</v>
+        <v>1.2889279932688499E-2</v>
       </c>
       <c r="F4">
-        <v>2.51812791824341</v>
+        <v>2.6078088283538801</v>
       </c>
       <c r="G4">
-        <v>1.3624031347506</v>
+        <v>1.3509799120684201</v>
       </c>
       <c r="H4">
-        <v>5.6188243845289403</v>
+        <v>5.3201697924214804</v>
       </c>
       <c r="I4">
-        <v>8.5735742204257903</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8.4317726744758303</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.8429000000000002E-3</v>
+        <v>2.9244000000000002E-3</v>
       </c>
       <c r="C5">
-        <v>2.3357800601225302E-3</v>
+        <v>1.8910141798962E-3</v>
       </c>
       <c r="D5">
-        <v>8.5977909972506702E-3</v>
+        <v>8.2698920145266308E-3</v>
       </c>
       <c r="E5">
-        <v>1.5512113572628701E-2</v>
+        <v>1.58488238379338E-2</v>
       </c>
       <c r="F5">
-        <v>1.64333379268646</v>
+        <v>1.7329246997833301</v>
       </c>
       <c r="G5">
-        <v>1.0294393229276799</v>
+        <v>0.87896743882667405</v>
       </c>
       <c r="H5">
-        <v>3.9602856314346302</v>
+        <v>3.8143227300089602</v>
       </c>
       <c r="I5">
-        <v>7.0622775916316201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.1392056984441998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5.7181000000000003E-2</v>
+        <v>5.6640000000000003E-2</v>
       </c>
       <c r="C6">
-        <v>4.9334153410666597E-2</v>
+        <v>4.8172269192872902E-2</v>
       </c>
       <c r="D6">
-        <v>7.2467065642694103E-2</v>
+        <v>7.0745863016412502E-2</v>
       </c>
       <c r="E6">
-        <v>9.1641895746959204E-2</v>
+        <v>9.0151562005582206E-2</v>
       </c>
       <c r="F6">
-        <v>9.8026046752929705</v>
+        <v>9.8819150924682599</v>
       </c>
       <c r="G6">
-        <v>8.0190934875790401</v>
+        <v>7.9280497496760196</v>
       </c>
       <c r="H6">
-        <v>11.752116301518599</v>
+        <v>11.697973877989901</v>
       </c>
       <c r="I6">
-        <v>15.3242432319462</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15.208344869849901</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>4.058E-3</v>
+        <v>3.9547000000000002E-3</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>2.2321876234644598E-3</v>
+        <v>2.3550612093284E-3</v>
       </c>
       <c r="E7">
-        <v>5.7730190604051504E-3</v>
+        <v>5.7417644794392399E-3</v>
       </c>
       <c r="F7">
-        <v>10.9411973953247</v>
+        <v>10.973635673522899</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>5.3936813807360497</v>
+        <v>5.76228437000099</v>
       </c>
       <c r="I7">
-        <v>15.3344373977435</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15.4976043428669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2345,25 +2319,25 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1.3128671377419601E-3</v>
+        <v>1.21985218896238E-3</v>
       </c>
       <c r="E8">
-        <v>5.0473929488978799E-3</v>
+        <v>5.1781039110402197E-3</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>8.0624386668205303E-2</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1.41996686952176</v>
+        <v>1.4229976285774</v>
       </c>
       <c r="I8">
-        <v>5.3077868955735203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.4838101261602903</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2374,25 +2348,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>6.1087107342125196E-4</v>
+        <v>5.7439306581203895E-4</v>
       </c>
       <c r="E9">
-        <v>1.92909504561727E-3</v>
+        <v>2.0821315438309999E-3</v>
       </c>
       <c r="F9">
-        <v>0.183493956923485</v>
+        <v>0.256727635860443</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>1.43101150657108</v>
+        <v>1.35555324957667</v>
       </c>
       <c r="I9">
-        <v>4.3865135279888499</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.9574188029660302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2403,228 +2377,228 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>4.7557744243577099E-4</v>
+        <v>4.3982304272650999E-4</v>
       </c>
       <c r="E10">
-        <v>3.8694066844688398E-3</v>
+        <v>4.74055656670471E-3</v>
       </c>
       <c r="F10">
-        <v>0.302094876766205</v>
+        <v>0.350065678358078</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0.40712779464749699</v>
+        <v>0.38196935998688297</v>
       </c>
       <c r="I10">
-        <v>3.3050997621347999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.051505064373</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>3.4808E-3</v>
+        <v>3.6608000000000001E-3</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1.6576823096817801E-2</v>
+        <v>1.5601994629628701E-2</v>
       </c>
       <c r="E11">
-        <v>3.0715937229705399E-2</v>
+        <v>2.7937013393169001E-2</v>
       </c>
       <c r="F11">
-        <v>1.7186236381530799</v>
+        <v>1.73536205291748</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>5.9935669648071004</v>
+        <v>5.7198678330092196</v>
       </c>
       <c r="I11">
-        <v>11.151286216633199</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>10.640823447945801</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.0553999999999999E-2</v>
+        <v>2.0627E-2</v>
       </c>
       <c r="C12">
-        <v>1.40822925402145E-2</v>
+        <v>1.3003388727424899E-2</v>
       </c>
       <c r="D12">
-        <v>4.2575006438859697E-2</v>
+        <v>4.0187217054950299E-2</v>
       </c>
       <c r="E12">
-        <v>5.6255397384596798E-2</v>
+        <v>5.3204026033178801E-2</v>
       </c>
       <c r="F12">
-        <v>5.4284100532531703</v>
+        <v>5.4471745491027797</v>
       </c>
       <c r="G12">
-        <v>3.27566375847189</v>
+        <v>3.16269209400929</v>
       </c>
       <c r="H12">
-        <v>9.7345476815118008</v>
+        <v>9.4510541535965604</v>
       </c>
       <c r="I12">
-        <v>13.464816207028299</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>13.0579777472147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.0638E-2</v>
+        <v>1.0432E-2</v>
       </c>
       <c r="C13">
-        <v>2.6141872696734E-3</v>
+        <v>1.67497964278755E-3</v>
       </c>
       <c r="D13">
-        <v>9.3779969811322601E-3</v>
+        <v>9.4408995757813297E-3</v>
       </c>
       <c r="E13">
-        <v>1.42473002615845E-2</v>
+        <v>1.4362937813285501E-2</v>
       </c>
       <c r="F13">
-        <v>14.174822807311999</v>
+        <v>14.265911102294901</v>
       </c>
       <c r="G13">
-        <v>2.9465067263084102</v>
+        <v>1.95208555359268</v>
       </c>
       <c r="H13">
-        <v>12.102288286894</v>
+        <v>12.4352772508584</v>
       </c>
       <c r="I13">
-        <v>18.9761837103222</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>19.9923621698319</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.2338E-2</v>
+        <v>1.2038999999999999E-2</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>8.9384279456321703E-3</v>
+        <v>8.7896100523205904E-3</v>
       </c>
       <c r="E14">
-        <v>1.55858250598239E-2</v>
+        <v>1.44353093364989E-2</v>
       </c>
       <c r="F14">
-        <v>11.9531354904175</v>
+        <v>12.0029945373535</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>8.6866971662097701</v>
+        <v>8.7892263989279797</v>
       </c>
       <c r="I14">
-        <v>15.5617279222066</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15.1419940411997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>8.711E-3</v>
+        <v>8.4040999999999994E-3</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1.0797323291863699E-3</v>
+        <v>2.34308584015542E-3</v>
       </c>
       <c r="E15">
-        <v>1.31541806771358E-2</v>
+        <v>1.22681412557289E-2</v>
       </c>
       <c r="F15">
-        <v>6.9539051055908203</v>
+        <v>6.9003849029540998</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0.81713819611392102</v>
+        <v>1.92949191300203</v>
       </c>
       <c r="I15">
-        <v>10.290586830855499</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9.6773137541245706</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>8.1490999999999994E-3</v>
+        <v>7.9638999999999995E-3</v>
       </c>
       <c r="C16">
-        <v>2.5639814256367701E-3</v>
+        <v>2.3563482153635602E-3</v>
       </c>
       <c r="D16">
-        <v>6.3323970680713802E-3</v>
+        <v>6.37467330715081E-3</v>
       </c>
       <c r="E16">
-        <v>1.0638032954393299E-2</v>
+        <v>1.03061500696736E-2</v>
       </c>
       <c r="F16">
-        <v>7.4613366127014196</v>
+        <v>7.4322819709777797</v>
       </c>
       <c r="G16">
-        <v>2.2170893409480001</v>
+        <v>2.0755146029155198</v>
       </c>
       <c r="H16">
-        <v>5.5547449778975704</v>
+        <v>5.6264619866313597</v>
       </c>
       <c r="I16">
-        <v>9.4305210489655895</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9.2083340700471101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>9.4062E-3</v>
+        <v>9.3907999999999995E-3</v>
       </c>
       <c r="C17">
-        <v>7.78863682279567E-3</v>
+        <v>7.08345081766817E-3</v>
       </c>
       <c r="D17">
-        <v>1.7267379181917199E-2</v>
+        <v>1.63653636881817E-2</v>
       </c>
       <c r="E17">
-        <v>2.2415956090301802E-2</v>
+        <v>2.1254857244073701E-2</v>
       </c>
       <c r="F17">
-        <v>4.1147699356079102</v>
+        <v>4.1229505538940403</v>
       </c>
       <c r="G17">
-        <v>2.9757533665118201</v>
+        <v>2.7088958117924502</v>
       </c>
       <c r="H17">
-        <v>6.4933602489371403</v>
+        <v>6.2229981810992703</v>
       </c>
       <c r="I17">
-        <v>8.7268142910058408</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8.44532016284702</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2638,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>3.8726396881032998E-3</v>
+        <v>2.9720686305313199E-3</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2650,213 +2624,213 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>1.8057906447577301</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.27628186294602</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2.8761999999999999E-2</v>
+        <v>2.8457E-2</v>
       </c>
       <c r="C19">
-        <v>2.6623147610777598E-2</v>
+        <v>2.4266307987596301E-2</v>
       </c>
       <c r="D19">
-        <v>3.9603080480139302E-2</v>
+        <v>3.7912168434118598E-2</v>
       </c>
       <c r="E19">
-        <v>4.9829949561673498E-2</v>
+        <v>4.6549808590375698E-2</v>
       </c>
       <c r="F19">
-        <v>5.3288946151733398</v>
+        <v>5.3225793838501003</v>
       </c>
       <c r="G19">
-        <v>4.3996563734535403</v>
+        <v>4.2216666722738303</v>
       </c>
       <c r="H19">
-        <v>6.6709421630071999</v>
+        <v>6.4341791082163198</v>
       </c>
       <c r="I19">
-        <v>8.4229085823339496</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8.1261942161237197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.13553000000000001</v>
+        <v>0.13319</v>
       </c>
       <c r="C20">
-        <v>0.10685346682453301</v>
+        <v>0.101164188033926</v>
       </c>
       <c r="D20">
-        <v>0.13158311948403001</v>
+        <v>0.12927709792942299</v>
       </c>
       <c r="E20">
-        <v>0.149683126706081</v>
+        <v>0.14590280363711999</v>
       </c>
       <c r="F20">
-        <v>16.889762878418001</v>
+        <v>16.8426322937012</v>
       </c>
       <c r="G20">
-        <v>12.9075551847776</v>
+        <v>12.929179008045899</v>
       </c>
       <c r="H20">
-        <v>16.001308272043499</v>
+        <v>15.9703131421868</v>
       </c>
       <c r="I20">
-        <v>18.5066713179997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>18.385162353691101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.27683999999999997</v>
+        <v>0.27252999999999999</v>
       </c>
       <c r="C21">
-        <v>0.23646182514893699</v>
+        <v>0.21351880332828599</v>
       </c>
       <c r="D21">
-        <v>0.28911931985476202</v>
+        <v>0.28463266513603602</v>
       </c>
       <c r="E21">
-        <v>0.32304371801828602</v>
+        <v>0.31826541746607501</v>
       </c>
       <c r="F21">
-        <v>13.3336801528931</v>
+        <v>13.298243522644</v>
       </c>
       <c r="G21">
-        <v>10.9968637437266</v>
+        <v>10.181134382833299</v>
       </c>
       <c r="H21">
-        <v>13.291533638767801</v>
+        <v>13.2879397965766</v>
       </c>
       <c r="I21">
-        <v>15.216919504651599</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15.3015173427658</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>4.9152000000000001E-2</v>
+        <v>4.8136999999999999E-2</v>
       </c>
       <c r="C22">
-        <v>2.2620343694298401E-2</v>
+        <v>2.2519500388349298E-2</v>
       </c>
       <c r="D22">
-        <v>3.7851711701442602E-2</v>
+        <v>3.9960997160736103E-2</v>
       </c>
       <c r="E22">
-        <v>6.9154588648416601E-2</v>
+        <v>6.8692209459880596E-2</v>
       </c>
       <c r="F22">
-        <v>34.082267761230497</v>
+        <v>33.9259033203125</v>
       </c>
       <c r="G22">
-        <v>14.457766826024899</v>
+        <v>14.7935570772412</v>
       </c>
       <c r="H22">
-        <v>25.399771291842601</v>
+        <v>26.719150064729</v>
       </c>
       <c r="I22">
-        <v>49.135579795094102</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>49.866543881557902</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>3.9974999999999997E-2</v>
+        <v>3.8873999999999999E-2</v>
       </c>
       <c r="C23">
-        <v>9.7740436105545198E-3</v>
+        <v>1.1217104418002199E-2</v>
       </c>
       <c r="D23">
-        <v>2.5649697341248098E-2</v>
+        <v>2.6431960360582402E-2</v>
       </c>
       <c r="E23">
-        <v>5.0183058278950199E-2</v>
+        <v>4.8661515950257403E-2</v>
       </c>
       <c r="F23">
-        <v>6.7317361831665004</v>
+        <v>6.6735706329345703</v>
       </c>
       <c r="G23">
-        <v>1.6367490443428501</v>
+        <v>1.9281339327782501</v>
       </c>
       <c r="H23">
-        <v>4.1079447867565504</v>
+        <v>4.3915959206499497</v>
       </c>
       <c r="I23">
-        <v>7.8441418673368002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.8963316840523703</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.0347E-3</v>
+        <v>2.0116000000000001E-3</v>
       </c>
       <c r="C24">
-        <v>1.0908404126708899E-3</v>
+        <v>1.11399489266036E-3</v>
       </c>
       <c r="D24">
-        <v>2.40408548333683E-3</v>
+        <v>2.3472499272360701E-3</v>
       </c>
       <c r="E24">
-        <v>3.9936359268895397E-3</v>
+        <v>3.8099668960330201E-3</v>
       </c>
       <c r="F24">
-        <v>14.1074895858765</v>
+        <v>14.0718631744385</v>
       </c>
       <c r="G24">
-        <v>6.2567204342083098</v>
+        <v>6.8838649363507498</v>
       </c>
       <c r="H24">
-        <v>14.9297900373203</v>
+        <v>14.5950906543821</v>
       </c>
       <c r="I24">
-        <v>26.470924526797699</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24.985751906782099</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.14742</v>
+        <v>0.14441999999999999</v>
       </c>
       <c r="C25">
-        <v>8.3831661394552101E-2</v>
+        <v>8.8675521994454706E-2</v>
       </c>
       <c r="D25">
-        <v>0.117287411538105</v>
+        <v>0.11768023350045501</v>
       </c>
       <c r="E25">
-        <v>0.16863696708333401</v>
+        <v>0.17182859799261399</v>
       </c>
       <c r="F25">
-        <v>53.0390434265137</v>
+        <v>53.074333190917997</v>
       </c>
       <c r="G25">
-        <v>31.4171460641419</v>
+        <v>32.576627397523097</v>
       </c>
       <c r="H25">
-        <v>45.115575811814601</v>
+        <v>46.9120689689831</v>
       </c>
       <c r="I25">
-        <v>57.210974035725201</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+        <v>58.449235986027396</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2870,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>7.90383263212314E-4</v>
+        <v>9.5754296738260103E-4</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -2882,36 +2856,36 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>3.16343805406057</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.0551255523154897</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.10508000000000001</v>
+        <v>0.10304000000000001</v>
       </c>
       <c r="C27">
-        <v>6.8371952250723206E-2</v>
+        <v>6.9450992070535594E-2</v>
       </c>
       <c r="D27">
-        <v>8.9506657326629296E-2</v>
+        <v>8.8290970790034007E-2</v>
       </c>
       <c r="E27">
-        <v>0.119131162550652</v>
+        <v>0.12066882772088799</v>
       </c>
       <c r="F27">
-        <v>87.859771728515597</v>
+        <v>87.883804321289105</v>
       </c>
       <c r="G27">
-        <v>65.439340922741707</v>
+        <v>67.368868536115897</v>
       </c>
       <c r="H27">
-        <v>80.357294846981304</v>
+        <v>81.302415543828701</v>
       </c>
       <c r="I27">
-        <v>88.518476672364898</v>
+        <v>89.349357528598404</v>
       </c>
     </row>
   </sheetData>
@@ -2920,11 +2894,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{915C8AEA-BA7B-428E-86C9-2CBD4786A0B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C27A059-B9D6-4C43-950F-CA7EAB9CB402}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2953,758 +2927,758 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.50748000000000004</v>
+        <v>0.14759</v>
       </c>
       <c r="C2">
-        <v>0.37071565010266999</v>
+        <v>9.3053148914197401E-2</v>
       </c>
       <c r="D2">
-        <v>0.47248930509695503</v>
+        <v>0.15185434391354799</v>
       </c>
       <c r="E2">
-        <v>0.54965526537902998</v>
+        <v>0.20402312997004701</v>
       </c>
       <c r="F2">
-        <v>47.626781463622997</v>
+        <v>14.839266777038601</v>
       </c>
       <c r="G2">
-        <v>37.839328719858599</v>
+        <v>9.4648488978269096</v>
       </c>
       <c r="H2">
-        <v>46.376341448226398</v>
+        <v>14.931919196284801</v>
       </c>
       <c r="I2">
-        <v>53.101767174494299</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>20.412331864621201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.14940999999999999</v>
+        <v>1.1355000000000001E-2</v>
       </c>
       <c r="C3">
-        <v>0.11059614682270801</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0.144703628565403</v>
+        <v>1.3252816513134201E-2</v>
       </c>
       <c r="E3">
-        <v>0.183749615105399</v>
+        <v>2.4349496217890301E-2</v>
       </c>
       <c r="F3">
-        <v>35.324127197265597</v>
+        <v>3.4414489269256601</v>
       </c>
       <c r="G3">
-        <v>29.367157982230498</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>36.808571735189602</v>
+        <v>3.4460954599807399</v>
       </c>
       <c r="I3">
-        <v>44.7226961211963</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.1821751659100599</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>7.7374999999999999E-2</v>
+        <v>1.8356999999999998E-2</v>
       </c>
       <c r="C4">
-        <v>5.8546015425406703E-2</v>
+        <v>1.38768370143234E-2</v>
       </c>
       <c r="D4">
-        <v>7.2848274786981096E-2</v>
+        <v>1.8737030322873799E-2</v>
       </c>
       <c r="E4">
-        <v>8.1513448178030704E-2</v>
+        <v>2.47141070794221E-2</v>
       </c>
       <c r="F4">
-        <v>48.023754119872997</v>
+        <v>12.270834922790501</v>
       </c>
       <c r="G4">
-        <v>40.611234741603703</v>
+        <v>9.0135326270206608</v>
       </c>
       <c r="H4">
-        <v>47.323777418322202</v>
+        <v>12.374673649771401</v>
       </c>
       <c r="I4">
-        <v>52.094762654234799</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>16.948578992146299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>9.7423999999999997E-2</v>
+        <v>3.4206E-2</v>
       </c>
       <c r="C5">
-        <v>6.7335367071421598E-2</v>
+        <v>2.14100987870115E-2</v>
       </c>
       <c r="D5">
-        <v>9.1606409788129395E-2</v>
+        <v>3.4329480289283398E-2</v>
       </c>
       <c r="E5">
-        <v>0.109910788830221</v>
+        <v>5.1850284901643597E-2</v>
       </c>
       <c r="F5">
-        <v>42.265460968017599</v>
+        <v>15.6521644592285</v>
       </c>
       <c r="G5">
-        <v>32.2287318895456</v>
+        <v>9.8388521632185704</v>
       </c>
       <c r="H5">
-        <v>41.222584887048697</v>
+        <v>15.529256867566099</v>
       </c>
       <c r="I5">
-        <v>47.817653016512203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24.346471985292801</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.28255000000000002</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.22088580490620499</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0.26729286337691399</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.33022490014524902</v>
+        <v>2.7827231602311001E-2</v>
       </c>
       <c r="F6">
-        <v>43.551502227783203</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>38.400880159315399</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>43.836620210597502</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>50.150823164446699</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.1705792400175499</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3.4978000000000001E-3</v>
+        <v>8.0359999999999997E-3</v>
       </c>
       <c r="C7">
-        <v>1.2720762794963E-3</v>
+        <v>3.1126466125203402E-3</v>
       </c>
       <c r="D7">
-        <v>3.5552738946248502E-3</v>
+        <v>7.0167985766605304E-3</v>
       </c>
       <c r="E7">
-        <v>1.92505634813122E-2</v>
+        <v>1.4219837067189999E-2</v>
       </c>
       <c r="F7">
-        <v>8.2788763046264595</v>
+        <v>21.293577194213899</v>
       </c>
       <c r="G7">
-        <v>3.0379135248911902</v>
+        <v>7.9550447375377997</v>
       </c>
       <c r="H7">
-        <v>9.1949513045186908</v>
+        <v>18.540161491480301</v>
       </c>
       <c r="I7">
-        <v>46.916994348303497</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>35.017790225042098</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>3.3820999999999997E-2</v>
+        <v>2.3085999999999999E-2</v>
       </c>
       <c r="C8">
-        <v>2.2193076057018101E-2</v>
+        <v>1.45060213961001E-2</v>
       </c>
       <c r="D8">
-        <v>3.1828098749908898E-2</v>
+        <v>2.2026713273570898E-2</v>
       </c>
       <c r="E8">
-        <v>4.05256733339922E-2</v>
+        <v>2.98123544277035E-2</v>
       </c>
       <c r="F8">
-        <v>36.226005554199197</v>
+        <v>24.741432189941399</v>
       </c>
       <c r="G8">
-        <v>26.058525615099899</v>
+        <v>16.430682286633601</v>
       </c>
       <c r="H8">
-        <v>34.5799186639493</v>
+        <v>24.161626654141301</v>
       </c>
       <c r="I8">
-        <v>42.376289373574302</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>34.608016800620099</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.6667999999999999E-2</v>
+        <v>1.218E-2</v>
       </c>
       <c r="C9">
-        <v>1.1402296766672201E-2</v>
+        <v>9.1146903685527907E-3</v>
       </c>
       <c r="D9">
-        <v>1.5641320860357501E-2</v>
+        <v>1.18243130792169E-2</v>
       </c>
       <c r="E9">
-        <v>2.0165454679764001E-2</v>
+        <v>1.43302014744261E-2</v>
       </c>
       <c r="F9">
-        <v>38.194236755371101</v>
+        <v>28.034254074096701</v>
       </c>
       <c r="G9">
-        <v>29.037270742508099</v>
+        <v>21.9247065315285</v>
       </c>
       <c r="H9">
-        <v>36.550127110376899</v>
+        <v>27.821312875619601</v>
       </c>
       <c r="I9">
-        <v>43.286174479860001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>34.7996680570389</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>3.5090000000000003E-2</v>
+        <v>4.1688999999999997E-2</v>
       </c>
       <c r="C10">
-        <v>2.3263914964454499E-2</v>
+        <v>3.03507165688915E-2</v>
       </c>
       <c r="D10">
-        <v>3.3857689725934503E-2</v>
+        <v>4.0317416271777103E-2</v>
       </c>
       <c r="E10">
-        <v>4.7922008262488699E-2</v>
+        <v>5.0130486740073602E-2</v>
       </c>
       <c r="F10">
-        <v>29.765403747558601</v>
+        <v>35.1049995422363</v>
       </c>
       <c r="G10">
-        <v>21.174921511954299</v>
+        <v>26.895345816787</v>
       </c>
       <c r="H10">
-        <v>28.9818645927955</v>
+        <v>34.440093681635403</v>
       </c>
       <c r="I10">
-        <v>37.214706355887103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>43.984109093843102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.17102000000000001</v>
+        <v>6.8831000000000003E-2</v>
       </c>
       <c r="C11">
-        <v>0.117620243622118</v>
+        <v>3.9387026593712203E-2</v>
       </c>
       <c r="D11">
-        <v>0.15782839274499399</v>
+        <v>6.8746551475692697E-2</v>
       </c>
       <c r="E11">
-        <v>0.184275852397351</v>
+        <v>7.7002111296005898E-2</v>
       </c>
       <c r="F11">
-        <v>56.321361541747997</v>
+        <v>24.762153625488299</v>
       </c>
       <c r="G11">
-        <v>44.334391256579401</v>
+        <v>14.9494388132232</v>
       </c>
       <c r="H11">
-        <v>54.094275774526103</v>
+        <v>24.7989605790128</v>
       </c>
       <c r="I11">
-        <v>69.713446241172207</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>27.671424642353301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.26556999999999997</v>
+        <v>8.2998000000000002E-2</v>
       </c>
       <c r="C12">
-        <v>0.23398655415233499</v>
+        <v>6.8016628426671596E-2</v>
       </c>
       <c r="D12">
-        <v>0.24904719319523699</v>
+        <v>8.4406640340914205E-2</v>
       </c>
       <c r="E12">
-        <v>0.26577694680772801</v>
+        <v>9.99987401049207E-2</v>
       </c>
       <c r="F12">
-        <v>58.677684783935497</v>
+        <v>20.136920928955099</v>
       </c>
       <c r="G12">
-        <v>53.902916302076498</v>
+        <v>15.844554796791501</v>
       </c>
       <c r="H12">
-        <v>57.975783991008797</v>
+        <v>19.8207046865266</v>
       </c>
       <c r="I12">
-        <v>65.337247138925093</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>25.1792925357346</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.7194999999999998E-2</v>
+        <v>1.2246E-3</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1.5698293318868201E-2</v>
+        <v>1.2970272995151001E-3</v>
       </c>
       <c r="E13">
-        <v>2.60144194581916E-2</v>
+        <v>3.1181270904657901E-2</v>
       </c>
       <c r="F13">
-        <v>23.128456115722699</v>
+        <v>1.44920122623444</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>21.2957472541285</v>
+        <v>1.78426731990236</v>
       </c>
       <c r="I13">
-        <v>34.749188626104697</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>33.046057570747898</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.0626E-2</v>
+        <v>2.6051000000000001E-2</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1.5762277308251998E-2</v>
       </c>
       <c r="D14">
-        <v>1.12031875983246E-2</v>
+        <v>2.4270835552404502E-2</v>
       </c>
       <c r="E14">
-        <v>2.68053591874945E-2</v>
+        <v>5.19080363116632E-2</v>
       </c>
       <c r="F14">
-        <v>12.610050201416</v>
+        <v>23.175512313842798</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>16.347508136556801</v>
       </c>
       <c r="H14">
-        <v>11.0335801480201</v>
+        <v>24.5921729263877</v>
       </c>
       <c r="I14">
-        <v>27.738419575879401</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>44.480727706856101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>7.7351000000000003E-2</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>5.0346653209714001E-2</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>7.6762825448533203E-2</v>
       </c>
       <c r="E15">
-        <v>5.5680006665368396E-3</v>
+        <v>9.6061501834591903E-2</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>59.655845642089801</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>42.086663081910203</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>60.655747620957797</v>
       </c>
       <c r="I15">
-        <v>4.3712679949518103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>71.822730556838906</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.5305000000000001E-2</v>
+        <v>5.1341999999999999E-2</v>
       </c>
       <c r="C16">
-        <v>1.8644362047706999E-2</v>
+        <v>4.2216730930427999E-2</v>
       </c>
       <c r="D16">
-        <v>2.5093217538648901E-2</v>
+        <v>5.0174414950466401E-2</v>
       </c>
       <c r="E16">
-        <v>3.1909478763689499E-2</v>
+        <v>5.8992927851272497E-2</v>
       </c>
       <c r="F16">
-        <v>21.6320705413818</v>
+        <v>44.872936248779297</v>
       </c>
       <c r="G16">
-        <v>15.367846677897299</v>
+        <v>39.068433206705599</v>
       </c>
       <c r="H16">
-        <v>22.004208183378601</v>
+        <v>44.617401652388203</v>
       </c>
       <c r="I16">
-        <v>27.782668277591299</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>50.479665869278698</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.12751000000000001</v>
+        <v>8.1762000000000001E-2</v>
       </c>
       <c r="C17">
-        <v>0.112260190816835</v>
+        <v>6.8751024034944805E-2</v>
       </c>
       <c r="D17">
-        <v>0.120103343717989</v>
+        <v>8.1748192540709905E-2</v>
       </c>
       <c r="E17">
-        <v>0.12839826407848501</v>
+        <v>8.7708674642641593E-2</v>
       </c>
       <c r="F17">
-        <v>45.734855651855497</v>
+        <v>31.463912963867202</v>
       </c>
       <c r="G17">
-        <v>42.169424301006501</v>
+        <v>27.722962679174</v>
       </c>
       <c r="H17">
-        <v>45.417662315687103</v>
+        <v>31.3543595615788</v>
       </c>
       <c r="I17">
-        <v>49.795280208457001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+        <v>33.548640087925797</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>7.6581999999999997E-2</v>
+        <v>0.10813</v>
       </c>
       <c r="C18">
-        <v>6.0370263367526003E-2</v>
+        <v>8.4122215392525096E-2</v>
       </c>
       <c r="D18">
-        <v>7.4308252775338507E-2</v>
+        <v>0.105233687928995</v>
       </c>
       <c r="E18">
-        <v>9.3549612639742402E-2</v>
+        <v>0.119389883333246</v>
       </c>
       <c r="F18">
-        <v>32.999385833740199</v>
+        <v>47.820888519287102</v>
       </c>
       <c r="G18">
-        <v>28.704103473096598</v>
+        <v>41.243070013707097</v>
       </c>
       <c r="H18">
-        <v>33.366302429351897</v>
+        <v>47.272975580069698</v>
       </c>
       <c r="I18">
-        <v>38.255763876615703</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>51.535461088511703</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.25463000000000002</v>
+        <v>0.20774999999999999</v>
       </c>
       <c r="C19">
-        <v>0.22217823051569199</v>
+        <v>0.17922307720457401</v>
       </c>
       <c r="D19">
-        <v>0.242097697396807</v>
+        <v>0.20611855057318801</v>
       </c>
       <c r="E19">
-        <v>0.2624880529177</v>
+        <v>0.221014153628149</v>
       </c>
       <c r="F19">
-        <v>40.5486030578613</v>
+        <v>35.308319091796903</v>
       </c>
       <c r="G19">
-        <v>37.303213100831897</v>
+        <v>32.041565069831599</v>
       </c>
       <c r="H19">
-        <v>40.628056635824201</v>
+        <v>35.115358041534201</v>
       </c>
       <c r="I19">
-        <v>44.446001894262103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+        <v>37.257293102150101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.31607000000000002</v>
+        <v>0.30264000000000002</v>
       </c>
       <c r="C20">
-        <v>0.26692926361685798</v>
+        <v>0.27242078135695702</v>
       </c>
       <c r="D20">
-        <v>0.30314360933419199</v>
+        <v>0.29996803775882502</v>
       </c>
       <c r="E20">
-        <v>0.35680963886273798</v>
+        <v>0.334915721991768</v>
       </c>
       <c r="F20">
-        <v>36.388057708740199</v>
+        <v>37.412242889404297</v>
       </c>
       <c r="G20">
-        <v>32.898435337664601</v>
+        <v>33.030422472645398</v>
       </c>
       <c r="H20">
-        <v>37.188936315661103</v>
+        <v>37.418539776420999</v>
       </c>
       <c r="I20">
-        <v>42.205768920790398</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>42.2037681037799</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.89959999999999996</v>
+        <v>0.65378999999999998</v>
       </c>
       <c r="C21">
-        <v>0.73646656969532498</v>
+        <v>0.58404866273979505</v>
       </c>
       <c r="D21">
-        <v>0.84311310230272496</v>
+        <v>0.65479543227798198</v>
       </c>
       <c r="E21">
-        <v>0.92485151779546904</v>
+        <v>0.75141155553411698</v>
       </c>
       <c r="F21">
-        <v>39.1140747070313</v>
+        <v>30.8067417144775</v>
       </c>
       <c r="G21">
-        <v>35.110197563988599</v>
+        <v>27.101201282839799</v>
       </c>
       <c r="H21">
-        <v>38.9642317536997</v>
+        <v>30.885777279356901</v>
       </c>
       <c r="I21">
-        <v>42.046943875295099</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+        <v>35.582644978116001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>3.4118000000000002E-2</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>2.2739508231045601E-2</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>3.3054571131182799E-2</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>6.03354302073612E-2</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>24.049392700195298</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>15.523135751597399</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>23.009797120919899</v>
       </c>
       <c r="I22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>35.390364104905402</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.10372000000000001</v>
+        <v>0.37597000000000003</v>
       </c>
       <c r="C23">
-        <v>6.8101127371213405E-2</v>
+        <v>0.297296659656207</v>
       </c>
       <c r="D23">
-        <v>0.108044119568633</v>
+        <v>0.36444579983681502</v>
       </c>
       <c r="E23">
-        <v>0.15555750744109401</v>
+        <v>0.40220384413001598</v>
       </c>
       <c r="F23">
-        <v>16.434352874755898</v>
+        <v>59.905647277832003</v>
       </c>
       <c r="G23">
-        <v>10.788560244723501</v>
+        <v>53.3076035368859</v>
       </c>
       <c r="H23">
-        <v>17.437336388122802</v>
+        <v>59.4917844046848</v>
       </c>
       <c r="I23">
-        <v>24.913869611733102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <v>63.779744561605099</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>8.1948000000000003E-3</v>
+        <v>8.9696000000000003E-4</v>
       </c>
       <c r="C24">
-        <v>5.3204235405127998E-3</v>
+        <v>1.8900091031231301E-4</v>
       </c>
       <c r="D24">
-        <v>7.8905519766549904E-3</v>
+        <v>1.02845823149316E-3</v>
       </c>
       <c r="E24">
-        <v>1.2174257680339201E-2</v>
+        <v>2.1142734806620499E-3</v>
       </c>
       <c r="F24">
-        <v>47.159008026122997</v>
+        <v>6.7769966125488299</v>
       </c>
       <c r="G24">
-        <v>34.626837193113097</v>
+        <v>1.2667655119779</v>
       </c>
       <c r="H24">
-        <v>49.404595694967199</v>
+        <v>6.2868281519438396</v>
       </c>
       <c r="I24">
-        <v>67.900610519371895</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+        <v>12.597623073803</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>8.4060000000000005E-4</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>7.8720559340239604E-4</v>
       </c>
       <c r="E25">
-        <v>9.4487029163835504E-3</v>
+        <v>3.14875963499494E-3</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>0.32407692074775701</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>0.30543650092237301</v>
       </c>
       <c r="I25">
-        <v>3.44202910550506</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1.33569903161651</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2.3819999999999999E-4</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>1.8501383313566299E-3</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>5.80496146535763E-3</v>
+        <v>5.3637582813045902E-4</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1.8181246519088701</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>7.8438076512546298</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>21.301508312669501</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.2490033387775599</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>1.2070000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>7.5654660061481704E-3</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>9.79048109238502E-3</v>
+        <v>6.0103606629487204E-4</v>
       </c>
       <c r="E27">
-        <v>2.2266616740758201E-2</v>
+        <v>3.481514406676E-3</v>
       </c>
       <c r="F27">
-        <v>8.7818155288696307</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>6.1701100920344496</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>8.9345402750889207</v>
+        <v>0.55630032270354002</v>
       </c>
       <c r="I27">
-        <v>16.554758045799801</v>
+        <v>2.69221783631082</v>
       </c>
     </row>
   </sheetData>
@@ -3713,11 +3687,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1231F6B2-80CF-4D9D-8028-35E57C26BC28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{922F880A-AF18-473B-9083-22EE5D6A6B71}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3746,181 +3720,181 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.10165</v>
+        <v>0.10014000000000001</v>
       </c>
       <c r="C2">
-        <v>7.1044134759279898E-2</v>
+        <v>7.8351260951475502E-2</v>
       </c>
       <c r="D2">
-        <v>0.107343462604629</v>
+        <v>0.10688316369074501</v>
       </c>
       <c r="E2">
-        <v>0.14630911241662001</v>
+        <v>0.149317485189399</v>
       </c>
       <c r="F2">
-        <v>11.9854431152344</v>
+        <v>12.047830581665</v>
       </c>
       <c r="G2">
-        <v>6.9162266215622603</v>
+        <v>7.6335421771234904</v>
       </c>
       <c r="H2">
-        <v>10.462169655659199</v>
+        <v>10.6841081799445</v>
       </c>
       <c r="I2">
-        <v>14.5767387884211</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15.2117423106488</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6.1929999999999999E-2</v>
+        <v>6.0920000000000002E-2</v>
       </c>
       <c r="C3">
-        <v>3.92407942345252E-2</v>
+        <v>3.5061555407812299E-2</v>
       </c>
       <c r="D3">
-        <v>6.8187491517629997E-2</v>
+        <v>6.5672824858144102E-2</v>
       </c>
       <c r="E3">
-        <v>0.10200996879027301</v>
+        <v>9.3479128403121794E-2</v>
       </c>
       <c r="F3">
-        <v>17.633205413818398</v>
+        <v>17.704687118530298</v>
       </c>
       <c r="G3">
-        <v>9.9302415751791298</v>
+        <v>8.7989703288713699</v>
       </c>
       <c r="H3">
-        <v>17.5518058572078</v>
+        <v>17.176365370705501</v>
       </c>
       <c r="I3">
-        <v>24.886194356638001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23.987971412528701</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.1726E-2</v>
+        <v>1.1540999999999999E-2</v>
       </c>
       <c r="C4">
-        <v>6.5636366112469102E-3</v>
+        <v>6.7826292892851203E-3</v>
       </c>
       <c r="D4">
-        <v>1.2148677338955E-2</v>
+        <v>1.2131641787337701E-2</v>
       </c>
       <c r="E4">
-        <v>1.8210167714821701E-2</v>
+        <v>1.7755962549764501E-2</v>
       </c>
       <c r="F4">
-        <v>9.6360912322997994</v>
+        <v>9.6801567077636701</v>
       </c>
       <c r="G4">
-        <v>4.2327881150877502</v>
+        <v>4.3652270304282599</v>
       </c>
       <c r="H4">
-        <v>7.8243608277804597</v>
+        <v>8.1046418815147501</v>
       </c>
       <c r="I4">
-        <v>11.9094645934418</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>11.837263157200599</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.3818E-2</v>
+        <v>1.3582E-2</v>
       </c>
       <c r="C5">
-        <v>8.4532213016146E-3</v>
+        <v>8.5487126455306307E-3</v>
       </c>
       <c r="D5">
-        <v>1.5856564434446899E-2</v>
+        <v>1.60514903998023E-2</v>
       </c>
       <c r="E5">
-        <v>2.62186268116778E-2</v>
+        <v>2.68386680387902E-2</v>
       </c>
       <c r="F5">
-        <v>7.7367024421691903</v>
+        <v>7.7651057243347203</v>
       </c>
       <c r="G5">
-        <v>3.7328859401135501</v>
+        <v>3.81162723927403</v>
       </c>
       <c r="H5">
-        <v>7.1381124053918903</v>
+        <v>7.3113001448857</v>
       </c>
       <c r="I5">
-        <v>12.4004886727319</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>12.6395682096367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9.7361000000000003E-2</v>
+        <v>9.5635999999999999E-2</v>
       </c>
       <c r="C6">
-        <v>5.9051431579440899E-2</v>
+        <v>5.9773833498139299E-2</v>
       </c>
       <c r="D6">
-        <v>0.106052868814211</v>
+        <v>0.104008997287465</v>
       </c>
       <c r="E6">
-        <v>0.15177438650591901</v>
+        <v>0.151786299758775</v>
       </c>
       <c r="F6">
-        <v>18.644126892089801</v>
+        <v>18.7100734710693</v>
       </c>
       <c r="G6">
-        <v>10.2711257896991</v>
+        <v>10.149213256431899</v>
       </c>
       <c r="H6">
-        <v>17.511947738499501</v>
+        <v>17.4990205780956</v>
       </c>
       <c r="I6">
-        <v>23.398055760344199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23.668230823702999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.0078000000000001E-3</v>
+        <v>1.9530999999999999E-3</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>3.3822508190830798E-3</v>
+        <v>3.0239131835346198E-3</v>
       </c>
       <c r="E7">
-        <v>8.8757559242368493E-3</v>
+        <v>8.5753362054511294E-3</v>
       </c>
       <c r="F7">
-        <v>4.120361328125</v>
+        <v>4.04728078842163</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6043853718301193</v>
+        <v>7.6399955053455804</v>
       </c>
       <c r="I7">
-        <v>22.261958040988201</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>21.093614832195499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3934,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3.7566604443184299E-3</v>
+        <v>4.0294983784953404E-3</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -3946,10 +3920,10 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>4.0956792407315703</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>4.60770134740652</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3963,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>1.6143035717348501E-3</v>
+        <v>1.57360411592056E-3</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -3975,10 +3949,10 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>3.7646959118740799</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3.8122980283449199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3989,112 +3963,112 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1.94215709928829E-3</v>
+        <v>1.96226140014412E-3</v>
       </c>
       <c r="E10">
-        <v>7.8088262575073996E-3</v>
+        <v>8.2108723249274106E-3</v>
       </c>
       <c r="F10">
-        <v>2.1229403093457201E-2</v>
+        <v>3.0141597613692301E-2</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>1.63298007089582</v>
+        <v>1.6829901621061001</v>
       </c>
       <c r="I10">
-        <v>7.1818767736476303</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.5259037401323399</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>3.4265999999999998E-2</v>
+        <v>3.4055000000000002E-2</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>2.4870937389486501E-2</v>
+        <v>2.65249723181143E-2</v>
       </c>
       <c r="E11">
-        <v>6.2927738003000097E-2</v>
+        <v>6.4194355757508106E-2</v>
       </c>
       <c r="F11">
-        <v>15.4918880462646</v>
+        <v>15.693783760070801</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>8.7084744172668902</v>
+        <v>9.9198897841112501</v>
       </c>
       <c r="I11">
-        <v>21.022391949361602</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>22.650665308506799</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>5.1976000000000001E-2</v>
+        <v>5.1292999999999998E-2</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>5.4045501262660001E-2</v>
+        <v>5.6700703555215601E-2</v>
       </c>
       <c r="E12">
-        <v>7.9293154297516294E-2</v>
+        <v>8.0053560201284596E-2</v>
       </c>
       <c r="F12">
-        <v>15.7830047607422</v>
+        <v>15.9021196365356</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>12.2918632755686</v>
+        <v>13.126893083980899</v>
       </c>
       <c r="I12">
-        <v>17.887990368388301</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>18.4867561050776</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>6.8998999999999996E-3</v>
+        <v>6.7786000000000001E-3</v>
       </c>
       <c r="C13">
-        <v>3.2521164720502601E-4</v>
+        <v>3.0518813547110999E-4</v>
       </c>
       <c r="D13">
-        <v>9.9472399882603695E-3</v>
+        <v>9.4806207499115395E-3</v>
       </c>
       <c r="E13">
-        <v>2.7899488114099799E-2</v>
+        <v>2.5515412676379901E-2</v>
       </c>
       <c r="F13">
-        <v>9.1248521804809606</v>
+        <v>9.1358356475830096</v>
       </c>
       <c r="G13">
-        <v>0.43089244213294697</v>
+        <v>0.41168630168299802</v>
       </c>
       <c r="H13">
-        <v>12.7043160204326</v>
+        <v>12.8536683882533</v>
       </c>
       <c r="I13">
-        <v>30.441738563043799</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>29.9070203288275</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -4108,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>2.4789667406152301E-2</v>
+        <v>2.54026920031768E-2</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -4120,10 +4094,10 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>21.321606386556901</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23.573859704469399</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4134,10 +4108,10 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>5.7402433331566203E-3</v>
+        <v>5.2084256138867999E-3</v>
       </c>
       <c r="E15">
-        <v>2.71193151082962E-2</v>
+        <v>2.3344510748921202E-2</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -4146,216 +4120,216 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>4.5302252312473303</v>
+        <v>4.2148042380513502</v>
       </c>
       <c r="I15">
-        <v>21.156904822783499</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>18.021322072161901</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>7.9944000000000005E-3</v>
+        <v>7.8732000000000003E-3</v>
       </c>
       <c r="C16">
-        <v>6.37433556288891E-3</v>
+        <v>6.27665067400249E-3</v>
       </c>
       <c r="D16">
-        <v>1.14424971608317E-2</v>
+        <v>1.1126502368391401E-2</v>
       </c>
       <c r="E16">
-        <v>2.0560329906828999E-2</v>
+        <v>1.8913620839302699E-2</v>
       </c>
       <c r="F16">
-        <v>7.3490552902221697</v>
+        <v>7.4056158065795898</v>
       </c>
       <c r="G16">
-        <v>5.6007707942632399</v>
+        <v>5.6708248604523801</v>
       </c>
       <c r="H16">
-        <v>9.9138222733508208</v>
+        <v>9.8111545448503197</v>
       </c>
       <c r="I16">
-        <v>17.291497384778399</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>16.7170057026192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2.6178E-2</v>
+        <v>2.5815999999999999E-2</v>
       </c>
       <c r="C17">
-        <v>1.0176744645117201E-2</v>
+        <v>1.050403965726E-2</v>
       </c>
       <c r="D17">
-        <v>2.9204152231922E-2</v>
+        <v>3.02139808377049E-2</v>
       </c>
       <c r="E17">
-        <v>4.1117760942179497E-2</v>
+        <v>4.1551092738852199E-2</v>
       </c>
       <c r="F17">
-        <v>12.1954555511475</v>
+        <v>12.2877292633057</v>
       </c>
       <c r="G17">
-        <v>4.0135857420357901</v>
+        <v>4.3014599547317696</v>
       </c>
       <c r="H17">
-        <v>10.853050027895099</v>
+        <v>11.4982877688043</v>
       </c>
       <c r="I17">
-        <v>15.112109854881099</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15.6041745813685</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.0522000000000001E-3</v>
+        <v>1.0671999999999999E-3</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>5.1685432141342202E-3</v>
+        <v>5.6563898502325002E-3</v>
       </c>
       <c r="E18">
-        <v>1.6893290419269898E-2</v>
+        <v>1.74521848163765E-2</v>
       </c>
       <c r="F18">
-        <v>2.0368185043335001</v>
+        <v>2.0868847370147701</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>2.26615246104158</v>
+        <v>2.5244214965457701</v>
       </c>
       <c r="I18">
-        <v>7.3263918905028396</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.6361776612967303</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>5.2308E-2</v>
+        <v>5.1596000000000003E-2</v>
       </c>
       <c r="C19">
-        <v>2.80122820405991E-2</v>
+        <v>2.73459315267028E-2</v>
       </c>
       <c r="D19">
-        <v>6.0790472036665197E-2</v>
+        <v>6.2839741165969604E-2</v>
       </c>
       <c r="E19">
-        <v>8.8625850786269597E-2</v>
+        <v>8.7052907294456305E-2</v>
       </c>
       <c r="F19">
-        <v>10.730725288391101</v>
+        <v>10.818879127502401</v>
       </c>
       <c r="G19">
-        <v>4.9421963505381603</v>
+        <v>4.9476887961125504</v>
       </c>
       <c r="H19">
-        <v>10.154008054457</v>
+        <v>10.560178874781201</v>
       </c>
       <c r="I19">
-        <v>14.302178069382499</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+        <v>14.466505657401999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>5.8058999999999999E-2</v>
+        <v>5.7155999999999998E-2</v>
       </c>
       <c r="C20">
-        <v>9.5884737373934104E-3</v>
+        <v>9.9609192057641405E-3</v>
       </c>
       <c r="D20">
-        <v>7.8409461733050898E-2</v>
+        <v>7.6868567366105894E-2</v>
       </c>
       <c r="E20">
-        <v>0.11173115900733201</v>
+        <v>0.107526072541424</v>
       </c>
       <c r="F20">
-        <v>9.3899879455566406</v>
+        <v>9.4538221359252894</v>
       </c>
       <c r="G20">
-        <v>1.1879486866048701</v>
+        <v>1.3633075756444799</v>
       </c>
       <c r="H20">
-        <v>9.4590530417312095</v>
+        <v>9.4282842834072902</v>
       </c>
       <c r="I20">
-        <v>13.260071616405201</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>13.175565696661501</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.26400000000000001</v>
+        <v>0.26016</v>
       </c>
       <c r="C21">
-        <v>0.18374057688821399</v>
+        <v>0.183890919357487</v>
       </c>
       <c r="D21">
-        <v>0.30199858147192099</v>
+        <v>0.298879829639629</v>
       </c>
       <c r="E21">
-        <v>0.37394684479738999</v>
+        <v>0.36024903600104902</v>
       </c>
       <c r="F21">
-        <v>14.2855882644653</v>
+        <v>14.391993522644</v>
       </c>
       <c r="G21">
-        <v>8.5259419445820193</v>
+        <v>8.6209399167691299</v>
       </c>
       <c r="H21">
-        <v>13.860657924803901</v>
+        <v>14.017106200482401</v>
       </c>
       <c r="I21">
-        <v>17.186702373337098</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17.045609816041399</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>6.1520999999999999E-2</v>
+        <v>6.0533000000000003E-2</v>
       </c>
       <c r="C22">
-        <v>2.4722530833182901E-2</v>
+        <v>2.6108291581369202E-2</v>
       </c>
       <c r="D22">
-        <v>7.0958574761318394E-2</v>
+        <v>6.6493957535860695E-2</v>
       </c>
       <c r="E22">
-        <v>0.112077585365415</v>
+        <v>0.11426239185999899</v>
       </c>
       <c r="F22">
-        <v>41.714073181152301</v>
+        <v>41.947227478027301</v>
       </c>
       <c r="G22">
-        <v>17.537124011998198</v>
+        <v>19.446537943715398</v>
       </c>
       <c r="H22">
-        <v>48.685173933578902</v>
+        <v>46.363752296288901</v>
       </c>
       <c r="I22">
-        <v>61.447508774933098</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>61.438514936965603</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -4366,112 +4340,112 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>1.7090297724082101E-2</v>
+        <v>1.7729899612627699E-2</v>
       </c>
       <c r="E23">
-        <v>5.7802483830983499E-2</v>
+        <v>5.6479942272048202E-2</v>
       </c>
       <c r="F23">
-        <v>0.23314584791660301</v>
+        <v>0.27130067348480202</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>2.8045723729813199</v>
+        <v>2.8746745821121999</v>
       </c>
       <c r="I23">
-        <v>8.8038147252714207</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <v>9.4765240899179393</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>3.9436000000000002E-3</v>
+        <v>3.8784000000000002E-3</v>
       </c>
       <c r="C24">
-        <v>8.8393110736128904E-4</v>
+        <v>7.7740464848622E-4</v>
       </c>
       <c r="D24">
-        <v>3.8761826041844899E-3</v>
+        <v>3.85100805822972E-3</v>
       </c>
       <c r="E24">
-        <v>6.3132168480059302E-3</v>
+        <v>5.8680963219402502E-3</v>
       </c>
       <c r="F24">
-        <v>29.070959091186499</v>
+        <v>29.125576019287099</v>
       </c>
       <c r="G24">
-        <v>5.9382028855719797</v>
+        <v>4.9793409429927697</v>
       </c>
       <c r="H24">
-        <v>24.072623951375199</v>
+        <v>24.6769775713441</v>
       </c>
       <c r="I24">
-        <v>35.973068853061598</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+        <v>36.131449786286403</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>9.6016000000000001E-3</v>
+        <v>9.3220000000000004E-3</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>1.4293206044627801E-2</v>
+        <v>1.24690018565071E-2</v>
       </c>
       <c r="E25">
-        <v>0.111602660799846</v>
+        <v>0.11015239753070701</v>
       </c>
       <c r="F25">
-        <v>3.2378766536712602</v>
+        <v>3.19921827316284</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>5.9168631133691196</v>
+        <v>5.2033904424194297</v>
       </c>
       <c r="I25">
-        <v>33.405348058872001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+        <v>33.553595987460703</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>1.6289000000000001E-2</v>
+        <v>1.6041E-2</v>
       </c>
       <c r="C26">
-        <v>1.0721637561306801E-2</v>
+        <v>1.01792976448879E-2</v>
       </c>
       <c r="D26">
-        <v>1.75334116822707E-2</v>
+        <v>1.7391628949183301E-2</v>
       </c>
       <c r="E26">
-        <v>3.3069807777574303E-2</v>
+        <v>3.3173267209029002E-2</v>
       </c>
       <c r="F26">
-        <v>78.321578979492202</v>
+        <v>78.507965087890597</v>
       </c>
       <c r="G26">
-        <v>62.270379543397098</v>
+        <v>60.054643434107597</v>
       </c>
       <c r="H26">
-        <v>78.481567686846603</v>
+        <v>80.151843407555006</v>
       </c>
       <c r="I26">
-        <v>90.290550905992006</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+        <v>90.774039865449595</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -4485,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>2.39983328626013E-2</v>
+        <v>2.3551612590954701E-2</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -4497,88 +4471,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>18.8997493190003</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7C53CE0-3DFA-034D-87C8-D94BA23282D4}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="16.1640625" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
+        <v>18.410734650678901</v>
       </c>
     </row>
   </sheetData>
